--- a/l4_feishu_ready.xlsx
+++ b/l4_feishu_ready.xlsx
@@ -891,17 +891,15 @@
           <t>1773371086904.png-1773371088304.png</t>
         </is>
       </c>
-      <c r="D2" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage1.png</t>
-        </is>
+      <c r="D2" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image1.png")</f>
+        <v/>
       </c>
       <c r="E2" s="57" t="n"/>
       <c r="F2" s="58" t="n"/>
-      <c r="G2" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage2.png</t>
-        </is>
+      <c r="G2" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image2.png")</f>
+        <v/>
       </c>
       <c r="H2" s="56" t="n"/>
       <c r="I2" s="1" t="inlineStr">
@@ -937,10 +935,9 @@
           <t>1773371097504.png</t>
         </is>
       </c>
-      <c r="D4" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage3.png</t>
-        </is>
+      <c r="D4" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image3.png")</f>
+        <v/>
       </c>
       <c r="E4" s="53" t="n"/>
       <c r="F4" s="54" t="n"/>
@@ -968,17 +965,15 @@
           <t>1773371099004.png - 1773371100005.png</t>
         </is>
       </c>
-      <c r="D5" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage4.png</t>
-        </is>
+      <c r="D5" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image4.png")</f>
+        <v/>
       </c>
       <c r="E5" s="53" t="n"/>
       <c r="F5" s="54" t="n"/>
-      <c r="G5" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage4.png</t>
-        </is>
+      <c r="G5" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image4.png")</f>
+        <v/>
       </c>
       <c r="H5" s="42" t="n"/>
       <c r="I5" s="7" t="inlineStr">
@@ -1003,17 +998,15 @@
           <t>1773371100005.png - 1773371100504.png</t>
         </is>
       </c>
-      <c r="D6" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage5.png</t>
-        </is>
+      <c r="D6" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image5.png")</f>
+        <v/>
       </c>
       <c r="E6" s="53" t="n"/>
       <c r="F6" s="54" t="n"/>
-      <c r="G6" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage4.png</t>
-        </is>
+      <c r="G6" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image4.png")</f>
+        <v/>
       </c>
       <c r="H6" s="42" t="n"/>
       <c r="I6" s="7" t="inlineStr">
@@ -1038,10 +1031,9 @@
           <t>1773371097504.png</t>
         </is>
       </c>
-      <c r="D7" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage3.png</t>
-        </is>
+      <c r="D7" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image3.png")</f>
+        <v/>
       </c>
       <c r="E7" s="53" t="n"/>
       <c r="F7" s="54" t="n"/>
@@ -1069,10 +1061,9 @@
           <t>1773371105505.png</t>
         </is>
       </c>
-      <c r="D8" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage6.png</t>
-        </is>
+      <c r="D8" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image6.png")</f>
+        <v/>
       </c>
       <c r="E8" s="53" t="n"/>
       <c r="F8" s="54" t="n"/>
@@ -1100,17 +1091,15 @@
           <t>1773371140005.png - 1773371141204.png</t>
         </is>
       </c>
-      <c r="D9" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage7.png</t>
-        </is>
+      <c r="D9" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image7.png")</f>
+        <v/>
       </c>
       <c r="E9" s="53" t="n"/>
       <c r="F9" s="54" t="n"/>
-      <c r="G9" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage8.png</t>
-        </is>
+      <c r="G9" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image8.png")</f>
+        <v/>
       </c>
       <c r="H9" s="42" t="n"/>
       <c r="I9" s="7" t="inlineStr">
@@ -1135,10 +1124,9 @@
           <t>1773371139204.png</t>
         </is>
       </c>
-      <c r="D10" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage9.png</t>
-        </is>
+      <c r="D10" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image9.png")</f>
+        <v/>
       </c>
       <c r="E10" s="53" t="n"/>
       <c r="F10" s="54" t="n"/>
@@ -1166,10 +1154,9 @@
           <t>1773371142905.png</t>
         </is>
       </c>
-      <c r="D11" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage10.png</t>
-        </is>
+      <c r="D11" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image10.png")</f>
+        <v/>
       </c>
       <c r="E11" s="57" t="n"/>
       <c r="F11" s="58" t="n"/>
@@ -1208,17 +1195,15 @@
           <t>1773371150604.png - 1773371151404.png</t>
         </is>
       </c>
-      <c r="D13" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage11.png</t>
-        </is>
+      <c r="D13" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image11.png")</f>
+        <v/>
       </c>
       <c r="E13" s="53" t="n"/>
       <c r="F13" s="54" t="n"/>
-      <c r="G13" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage12.png</t>
-        </is>
+      <c r="G13" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image12.png")</f>
+        <v/>
       </c>
       <c r="H13" s="42" t="n"/>
       <c r="I13" s="7" t="inlineStr">
@@ -1243,10 +1228,9 @@
           <t>1773371151603.png</t>
         </is>
       </c>
-      <c r="D14" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage13.png</t>
-        </is>
+      <c r="D14" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image13.png")</f>
+        <v/>
       </c>
       <c r="E14" s="53" t="n"/>
       <c r="F14" s="54" t="n"/>
@@ -1274,17 +1258,15 @@
           <t>1773371152605.png - 1773371153804.png</t>
         </is>
       </c>
-      <c r="D15" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage14.png</t>
-        </is>
+      <c r="D15" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image14.png")</f>
+        <v/>
       </c>
       <c r="E15" s="53" t="n"/>
       <c r="F15" s="54" t="n"/>
-      <c r="G15" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage15.png</t>
-        </is>
+      <c r="G15" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image15.png")</f>
+        <v/>
       </c>
       <c r="H15" s="42" t="n"/>
       <c r="I15" s="7" t="inlineStr">
@@ -1309,17 +1291,15 @@
           <t>1773371157005.png - 1773371157105.png</t>
         </is>
       </c>
-      <c r="D16" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage16.png</t>
-        </is>
+      <c r="D16" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image16.png")</f>
+        <v/>
       </c>
       <c r="E16" s="57" t="n"/>
       <c r="F16" s="58" t="n"/>
-      <c r="G16" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage17.png</t>
-        </is>
+      <c r="G16" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image17.png")</f>
+        <v/>
       </c>
       <c r="H16" s="56" t="n"/>
       <c r="I16" s="1" t="inlineStr">
@@ -1355,17 +1335,15 @@
           <t>1773371154804.png - 1773371157804.png</t>
         </is>
       </c>
-      <c r="D18" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage18.png</t>
-        </is>
+      <c r="D18" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image18.png")</f>
+        <v/>
       </c>
       <c r="E18" s="53" t="n"/>
       <c r="F18" s="54" t="n"/>
-      <c r="G18" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage16.png</t>
-        </is>
+      <c r="G18" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image16.png")</f>
+        <v/>
       </c>
       <c r="H18" s="42" t="n"/>
       <c r="I18" s="7" t="inlineStr">
@@ -1390,17 +1368,15 @@
           <t>1773371156904.png - 1773371158905.png</t>
         </is>
       </c>
-      <c r="D19" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage19.png</t>
-        </is>
+      <c r="D19" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image19.png")</f>
+        <v/>
       </c>
       <c r="E19" s="53" t="n"/>
       <c r="F19" s="54" t="n"/>
-      <c r="G19" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage20.png</t>
-        </is>
+      <c r="G19" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image20.png")</f>
+        <v/>
       </c>
       <c r="H19" s="42" t="n"/>
       <c r="I19" s="7" t="inlineStr">
@@ -1425,17 +1401,15 @@
           <t>1773371160004.png - 1773371161904.png</t>
         </is>
       </c>
-      <c r="D20" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage21.png</t>
-        </is>
+      <c r="D20" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image21.png")</f>
+        <v/>
       </c>
       <c r="E20" s="53" t="n"/>
       <c r="F20" s="54" t="n"/>
-      <c r="G20" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage22.png</t>
-        </is>
+      <c r="G20" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image22.png")</f>
+        <v/>
       </c>
       <c r="H20" s="42" t="n"/>
       <c r="I20" s="7" t="inlineStr">
@@ -1460,17 +1434,15 @@
           <t>1773371159004.png - 1773371159905.png</t>
         </is>
       </c>
-      <c r="D21" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage23.png</t>
-        </is>
+      <c r="D21" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image23.png")</f>
+        <v/>
       </c>
       <c r="E21" s="53" t="n"/>
       <c r="F21" s="54" t="n"/>
-      <c r="G21" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage24.png</t>
-        </is>
+      <c r="G21" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image24.png")</f>
+        <v/>
       </c>
       <c r="H21" s="42" t="n"/>
       <c r="I21" s="7" t="inlineStr">
@@ -1495,10 +1467,9 @@
           <t>1773371161804.png</t>
         </is>
       </c>
-      <c r="D22" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage25.png</t>
-        </is>
+      <c r="D22" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image25.png")</f>
+        <v/>
       </c>
       <c r="E22" s="53" t="n"/>
       <c r="F22" s="54" t="n"/>
@@ -1526,17 +1497,15 @@
           <t>1773371160004.png - 1773371161904.png</t>
         </is>
       </c>
-      <c r="D23" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage21.png</t>
-        </is>
+      <c r="D23" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image21.png")</f>
+        <v/>
       </c>
       <c r="E23" s="53" t="n"/>
       <c r="F23" s="54" t="n"/>
-      <c r="G23" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage22.png</t>
-        </is>
+      <c r="G23" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image22.png")</f>
+        <v/>
       </c>
       <c r="H23" s="42" t="n"/>
       <c r="I23" s="7" t="inlineStr">
@@ -1561,10 +1530,9 @@
           <t>1773371163205.png</t>
         </is>
       </c>
-      <c r="D24" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage26.png</t>
-        </is>
+      <c r="D24" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image26.png")</f>
+        <v/>
       </c>
       <c r="E24" s="53" t="n"/>
       <c r="F24" s="54" t="n"/>
@@ -1592,17 +1560,15 @@
           <t>1773371164205.png - 1773371165104.png</t>
         </is>
       </c>
-      <c r="D25" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage27.png</t>
-        </is>
+      <c r="D25" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image27.png")</f>
+        <v/>
       </c>
       <c r="E25" s="53" t="n"/>
       <c r="F25" s="54" t="n"/>
-      <c r="G25" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage28.png</t>
-        </is>
+      <c r="G25" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image28.png")</f>
+        <v/>
       </c>
       <c r="H25" s="42" t="n"/>
       <c r="I25" s="7" t="inlineStr">
@@ -1627,10 +1593,9 @@
           <t>1773371186705.png</t>
         </is>
       </c>
-      <c r="D26" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage29.png</t>
-        </is>
+      <c r="D26" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image29.png")</f>
+        <v/>
       </c>
       <c r="E26" s="53" t="n"/>
       <c r="F26" s="54" t="n"/>
@@ -1658,10 +1623,9 @@
           <t>1773371187105.png</t>
         </is>
       </c>
-      <c r="D27" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage30.png</t>
-        </is>
+      <c r="D27" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image30.png")</f>
+        <v/>
       </c>
       <c r="E27" s="53" t="n"/>
       <c r="F27" s="54" t="n"/>
@@ -1689,10 +1653,9 @@
           <t>1773371187205.png</t>
         </is>
       </c>
-      <c r="D28" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage31.png</t>
-        </is>
+      <c r="D28" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image31.png")</f>
+        <v/>
       </c>
       <c r="E28" s="53" t="n"/>
       <c r="F28" s="54" t="n"/>
@@ -1720,10 +1683,9 @@
           <t>1773371193304.png</t>
         </is>
       </c>
-      <c r="D29" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage32.png</t>
-        </is>
+      <c r="D29" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image32.png")</f>
+        <v/>
       </c>
       <c r="E29" s="53" t="n"/>
       <c r="F29" s="54" t="n"/>
@@ -1751,17 +1713,15 @@
           <t>1773371193805.png - 1773371194305.png</t>
         </is>
       </c>
-      <c r="D30" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage33.png</t>
-        </is>
+      <c r="D30" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image33.png")</f>
+        <v/>
       </c>
       <c r="E30" s="53" t="n"/>
       <c r="F30" s="54" t="n"/>
-      <c r="G30" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage34.png</t>
-        </is>
+      <c r="G30" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image34.png")</f>
+        <v/>
       </c>
       <c r="H30" s="42" t="n"/>
       <c r="I30" s="7" t="inlineStr">
@@ -1786,10 +1746,9 @@
           <t>1773371194904.png</t>
         </is>
       </c>
-      <c r="D31" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage35.png</t>
-        </is>
+      <c r="D31" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image35.png")</f>
+        <v/>
       </c>
       <c r="E31" s="53" t="n"/>
       <c r="F31" s="54" t="n"/>
@@ -1817,17 +1776,15 @@
           <t>1773371217804.png - 1773371219905.png</t>
         </is>
       </c>
-      <c r="D32" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage36.png</t>
-        </is>
+      <c r="D32" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image36.png")</f>
+        <v/>
       </c>
       <c r="E32" s="53" t="n"/>
       <c r="F32" s="54" t="n"/>
-      <c r="G32" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage37.png</t>
-        </is>
+      <c r="G32" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image37.png")</f>
+        <v/>
       </c>
       <c r="H32" s="42" t="n"/>
       <c r="I32" s="7" t="inlineStr">
@@ -1852,10 +1809,9 @@
           <t>1773371226404.png</t>
         </is>
       </c>
-      <c r="D33" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage38.png</t>
-        </is>
+      <c r="D33" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image38.png")</f>
+        <v/>
       </c>
       <c r="E33" s="53" t="n"/>
       <c r="F33" s="54" t="n"/>
@@ -1883,10 +1839,9 @@
           <t>1773371226805.png</t>
         </is>
       </c>
-      <c r="D34" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage39.png</t>
-        </is>
+      <c r="D34" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image39.png")</f>
+        <v/>
       </c>
       <c r="E34" s="53" t="n"/>
       <c r="F34" s="54" t="n"/>
@@ -1914,17 +1869,15 @@
           <t>1773371232604.png - 1773371233204.png</t>
         </is>
       </c>
-      <c r="D35" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage40.png</t>
-        </is>
+      <c r="D35" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image40.png")</f>
+        <v/>
       </c>
       <c r="E35" s="53" t="n"/>
       <c r="F35" s="54" t="n"/>
-      <c r="G35" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage41.png</t>
-        </is>
+      <c r="G35" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image41.png")</f>
+        <v/>
       </c>
       <c r="H35" s="42" t="n"/>
       <c r="I35" s="7" t="inlineStr">
@@ -1949,10 +1902,9 @@
           <t>1773371234104.png</t>
         </is>
       </c>
-      <c r="D36" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage42.png</t>
-        </is>
+      <c r="D36" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image42.png")</f>
+        <v/>
       </c>
       <c r="E36" s="53" t="n"/>
       <c r="F36" s="54" t="n"/>
@@ -1980,17 +1932,15 @@
           <t>1773371233304.png - 1773371234405.png</t>
         </is>
       </c>
-      <c r="D37" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage43.png</t>
-        </is>
+      <c r="D37" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image43.png")</f>
+        <v/>
       </c>
       <c r="E37" s="53" t="n"/>
       <c r="F37" s="54" t="n"/>
-      <c r="G37" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage44.png</t>
-        </is>
+      <c r="G37" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image44.png")</f>
+        <v/>
       </c>
       <c r="H37" s="42" t="n"/>
       <c r="I37" s="7" t="inlineStr">
@@ -2015,17 +1965,15 @@
           <t>1773371239005.png - 1773371239804.png</t>
         </is>
       </c>
-      <c r="D38" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage45.png</t>
-        </is>
+      <c r="D38" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image45.png")</f>
+        <v/>
       </c>
       <c r="E38" s="53" t="n"/>
       <c r="F38" s="54" t="n"/>
-      <c r="G38" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage46.png</t>
-        </is>
+      <c r="G38" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image46.png")</f>
+        <v/>
       </c>
       <c r="H38" s="42" t="n"/>
       <c r="I38" s="7" t="inlineStr">
@@ -2050,17 +1998,15 @@
           <t>1773371260705.png - 1773371261505.png</t>
         </is>
       </c>
-      <c r="D39" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage47.png</t>
-        </is>
+      <c r="D39" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image47.png")</f>
+        <v/>
       </c>
       <c r="E39" s="53" t="n"/>
       <c r="F39" s="54" t="n"/>
-      <c r="G39" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage48.png</t>
-        </is>
+      <c r="G39" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image48.png")</f>
+        <v/>
       </c>
       <c r="H39" s="42" t="n"/>
       <c r="I39" s="7" t="inlineStr">
@@ -2085,10 +2031,9 @@
           <t>1773371261705.png</t>
         </is>
       </c>
-      <c r="D40" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage49.png</t>
-        </is>
+      <c r="D40" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image49.png")</f>
+        <v/>
       </c>
       <c r="E40" s="53" t="n"/>
       <c r="F40" s="54" t="n"/>
@@ -2116,17 +2061,15 @@
           <t>1773371263704.png - 1773371264805.png</t>
         </is>
       </c>
-      <c r="D41" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage50.png</t>
-        </is>
+      <c r="D41" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image50.png")</f>
+        <v/>
       </c>
       <c r="E41" s="53" t="n"/>
       <c r="F41" s="54" t="n"/>
-      <c r="G41" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage51.png</t>
-        </is>
+      <c r="G41" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image51.png")</f>
+        <v/>
       </c>
       <c r="H41" s="42" t="n"/>
       <c r="I41" s="7" t="inlineStr">
@@ -2151,17 +2094,15 @@
           <t>1773371288004.png - 1773371288405.png</t>
         </is>
       </c>
-      <c r="D42" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage52.png</t>
-        </is>
+      <c r="D42" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image52.png")</f>
+        <v/>
       </c>
       <c r="E42" s="53" t="n"/>
       <c r="F42" s="54" t="n"/>
-      <c r="G42" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage53.png</t>
-        </is>
+      <c r="G42" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image53.png")</f>
+        <v/>
       </c>
       <c r="H42" s="42" t="n"/>
       <c r="I42" s="7" t="inlineStr">
@@ -2186,17 +2127,15 @@
           <t>1773371289604.png - 1773371290504.png</t>
         </is>
       </c>
-      <c r="D43" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage54.png</t>
-        </is>
+      <c r="D43" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image54.png")</f>
+        <v/>
       </c>
       <c r="E43" s="53" t="n"/>
       <c r="F43" s="54" t="n"/>
-      <c r="G43" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage55.png</t>
-        </is>
+      <c r="G43" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image55.png")</f>
+        <v/>
       </c>
       <c r="H43" s="42" t="n"/>
       <c r="I43" s="7" t="inlineStr">
@@ -2221,17 +2160,15 @@
           <t>1773371301705.png - 1773371302605.png</t>
         </is>
       </c>
-      <c r="D44" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage56.png</t>
-        </is>
+      <c r="D44" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image56.png")</f>
+        <v/>
       </c>
       <c r="E44" s="53" t="n"/>
       <c r="F44" s="54" t="n"/>
-      <c r="G44" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage57.png</t>
-        </is>
+      <c r="G44" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image57.png")</f>
+        <v/>
       </c>
       <c r="H44" s="42" t="n"/>
       <c r="I44" s="7" t="inlineStr">
@@ -2256,10 +2193,9 @@
           <t>1773371302904.png</t>
         </is>
       </c>
-      <c r="D45" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage58.png</t>
-        </is>
+      <c r="D45" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image58.png")</f>
+        <v/>
       </c>
       <c r="E45" s="53" t="n"/>
       <c r="F45" s="54" t="n"/>
@@ -2287,17 +2223,15 @@
           <t>1773371303704.png - 1773371304704.png</t>
         </is>
       </c>
-      <c r="D46" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage59.png</t>
-        </is>
+      <c r="D46" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image59.png")</f>
+        <v/>
       </c>
       <c r="E46" s="53" t="n"/>
       <c r="F46" s="54" t="n"/>
-      <c r="G46" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage60.png</t>
-        </is>
+      <c r="G46" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image60.png")</f>
+        <v/>
       </c>
       <c r="H46" s="42" t="n"/>
       <c r="I46" s="7" t="inlineStr">
@@ -2322,17 +2256,15 @@
           <t>1773371305905.png - 1773371306804.png</t>
         </is>
       </c>
-      <c r="D47" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage61.png</t>
-        </is>
+      <c r="D47" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image61.png")</f>
+        <v/>
       </c>
       <c r="E47" s="53" t="n"/>
       <c r="F47" s="54" t="n"/>
-      <c r="G47" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage62.png</t>
-        </is>
+      <c r="G47" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image62.png")</f>
+        <v/>
       </c>
       <c r="H47" s="42" t="n"/>
       <c r="I47" s="7" t="inlineStr">
@@ -2357,17 +2289,15 @@
           <t>1773371308004.png - 1773371308604.png</t>
         </is>
       </c>
-      <c r="D48" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage63.png</t>
-        </is>
+      <c r="D48" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image63.png")</f>
+        <v/>
       </c>
       <c r="E48" s="53" t="n"/>
       <c r="F48" s="54" t="n"/>
-      <c r="G48" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage64.png</t>
-        </is>
+      <c r="G48" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image64.png")</f>
+        <v/>
       </c>
       <c r="H48" s="42" t="n"/>
       <c r="I48" s="7" t="inlineStr">
@@ -2392,17 +2322,15 @@
           <t>1773371321405.png - 1773371322404.png</t>
         </is>
       </c>
-      <c r="D49" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage65.png</t>
-        </is>
+      <c r="D49" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image65.png")</f>
+        <v/>
       </c>
       <c r="E49" s="53" t="n"/>
       <c r="F49" s="54" t="n"/>
-      <c r="G49" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage66.png</t>
-        </is>
+      <c r="G49" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image66.png")</f>
+        <v/>
       </c>
       <c r="H49" s="42" t="n"/>
       <c r="I49" s="7" t="inlineStr">
@@ -2427,17 +2355,15 @@
           <t>1773371333204.png - 1773371335204.png</t>
         </is>
       </c>
-      <c r="D50" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage67.png</t>
-        </is>
+      <c r="D50" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image67.png")</f>
+        <v/>
       </c>
       <c r="E50" s="57" t="n"/>
       <c r="F50" s="58" t="n"/>
-      <c r="G50" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage68.png</t>
-        </is>
+      <c r="G50" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image68.png")</f>
+        <v/>
       </c>
       <c r="H50" s="56" t="n"/>
       <c r="I50" s="1" t="inlineStr">
@@ -2473,10 +2399,9 @@
           <t>1773371335505.png</t>
         </is>
       </c>
-      <c r="D52" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage69.png</t>
-        </is>
+      <c r="D52" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image69.png")</f>
+        <v/>
       </c>
       <c r="E52" s="53" t="n"/>
       <c r="F52" s="54" t="n"/>
@@ -2504,17 +2429,15 @@
           <t>1773371335904.png - 1773371336205.png</t>
         </is>
       </c>
-      <c r="D53" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage70.png</t>
-        </is>
+      <c r="D53" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image70.png")</f>
+        <v/>
       </c>
       <c r="E53" s="53" t="n"/>
       <c r="F53" s="54" t="n"/>
-      <c r="G53" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage71.png</t>
-        </is>
+      <c r="G53" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image71.png")</f>
+        <v/>
       </c>
       <c r="H53" s="42" t="n"/>
       <c r="I53" s="7" t="inlineStr">
@@ -2539,17 +2462,15 @@
           <t xml:space="preserve">1773371336305.png- 1773371337404.png </t>
         </is>
       </c>
-      <c r="D54" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage72.png</t>
-        </is>
+      <c r="D54" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image72.png")</f>
+        <v/>
       </c>
       <c r="E54" s="53" t="n"/>
       <c r="F54" s="54" t="n"/>
-      <c r="G54" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage73.png</t>
-        </is>
+      <c r="G54" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image73.png")</f>
+        <v/>
       </c>
       <c r="H54" s="42" t="n"/>
       <c r="I54" s="7" t="inlineStr">
@@ -2574,17 +2495,15 @@
           <t>1773371339605.png - 1773371341704.png</t>
         </is>
       </c>
-      <c r="D55" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage74.png</t>
-        </is>
+      <c r="D55" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image74.png")</f>
+        <v/>
       </c>
       <c r="E55" s="53" t="n"/>
       <c r="F55" s="54" t="n"/>
-      <c r="G55" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage75.png</t>
-        </is>
+      <c r="G55" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image75.png")</f>
+        <v/>
       </c>
       <c r="H55" s="42" t="n"/>
       <c r="I55" s="7" t="inlineStr">
@@ -2609,17 +2528,15 @@
           <t>1773371344005.png - 1773371344904.png</t>
         </is>
       </c>
-      <c r="D56" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage76.png</t>
-        </is>
+      <c r="D56" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image76.png")</f>
+        <v/>
       </c>
       <c r="E56" s="53" t="n"/>
       <c r="F56" s="54" t="n"/>
-      <c r="G56" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage77.png</t>
-        </is>
+      <c r="G56" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image77.png")</f>
+        <v/>
       </c>
       <c r="H56" s="42" t="n"/>
       <c r="I56" s="7" t="inlineStr">
@@ -2644,17 +2561,15 @@
           <t>1773371349705.png - 1773371350904.png</t>
         </is>
       </c>
-      <c r="D57" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage78.png</t>
-        </is>
+      <c r="D57" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image78.png")</f>
+        <v/>
       </c>
       <c r="E57" s="53" t="n"/>
       <c r="F57" s="54" t="n"/>
-      <c r="G57" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage79.png</t>
-        </is>
+      <c r="G57" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image79.png")</f>
+        <v/>
       </c>
       <c r="H57" s="42" t="n"/>
       <c r="I57" s="7" t="inlineStr">
@@ -2679,17 +2594,15 @@
           <t>1773371351804.png - 1773371353905.png</t>
         </is>
       </c>
-      <c r="D58" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage80.png</t>
-        </is>
+      <c r="D58" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image80.png")</f>
+        <v/>
       </c>
       <c r="E58" s="53" t="n"/>
       <c r="F58" s="54" t="n"/>
-      <c r="G58" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage81.png</t>
-        </is>
+      <c r="G58" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image81.png")</f>
+        <v/>
       </c>
       <c r="H58" s="42" t="n"/>
       <c r="I58" s="7" t="inlineStr">
@@ -2714,17 +2627,15 @@
           <t>1773371354005.png - 1773371355005.png</t>
         </is>
       </c>
-      <c r="D59" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage82.png</t>
-        </is>
+      <c r="D59" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image82.png")</f>
+        <v/>
       </c>
       <c r="E59" s="53" t="n"/>
       <c r="F59" s="54" t="n"/>
-      <c r="G59" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage83.png</t>
-        </is>
+      <c r="G59" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image83.png")</f>
+        <v/>
       </c>
       <c r="H59" s="42" t="n"/>
       <c r="I59" s="7" t="inlineStr">
@@ -2749,17 +2660,15 @@
           <t>1773371357305.png - 1773371358305.png</t>
         </is>
       </c>
-      <c r="D60" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage84.png</t>
-        </is>
+      <c r="D60" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image84.png")</f>
+        <v/>
       </c>
       <c r="E60" s="53" t="n"/>
       <c r="F60" s="54" t="n"/>
-      <c r="G60" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage85.png</t>
-        </is>
+      <c r="G60" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image85.png")</f>
+        <v/>
       </c>
       <c r="H60" s="42" t="n"/>
       <c r="I60" s="7" t="inlineStr">
@@ -2784,10 +2693,9 @@
           <t>1773371359704.png</t>
         </is>
       </c>
-      <c r="D61" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage86.png</t>
-        </is>
+      <c r="D61" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image86.png")</f>
+        <v/>
       </c>
       <c r="E61" s="53" t="n"/>
       <c r="F61" s="54" t="n"/>
@@ -2815,10 +2723,9 @@
           <t>1773371364104.png</t>
         </is>
       </c>
-      <c r="D62" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage87.png</t>
-        </is>
+      <c r="D62" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image87.png")</f>
+        <v/>
       </c>
       <c r="E62" s="53" t="n"/>
       <c r="F62" s="54" t="n"/>
@@ -2846,10 +2753,9 @@
           <t>1773371364505.png</t>
         </is>
       </c>
-      <c r="D63" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage88.png</t>
-        </is>
+      <c r="D63" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image88.png")</f>
+        <v/>
       </c>
       <c r="E63" s="53" t="n"/>
       <c r="F63" s="54" t="n"/>
@@ -2877,17 +2783,15 @@
           <t>1773371364805.png - 1773371365704.png</t>
         </is>
       </c>
-      <c r="D64" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage89.png</t>
-        </is>
+      <c r="D64" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image89.png")</f>
+        <v/>
       </c>
       <c r="E64" s="53" t="n"/>
       <c r="F64" s="54" t="n"/>
-      <c r="G64" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage90.png</t>
-        </is>
+      <c r="G64" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image90.png")</f>
+        <v/>
       </c>
       <c r="H64" s="42" t="n"/>
       <c r="I64" s="7" t="inlineStr">
@@ -2912,17 +2816,15 @@
           <t>1773371368004.png - 1773371368605.png</t>
         </is>
       </c>
-      <c r="D65" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage91.png</t>
-        </is>
+      <c r="D65" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image91.png")</f>
+        <v/>
       </c>
       <c r="E65" s="53" t="n"/>
       <c r="F65" s="54" t="n"/>
-      <c r="G65" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage92.png</t>
-        </is>
+      <c r="G65" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image92.png")</f>
+        <v/>
       </c>
       <c r="H65" s="42" t="n"/>
       <c r="I65" s="7" t="inlineStr">
@@ -2947,17 +2849,15 @@
           <t>1773371370905.png - 1773371371805.png</t>
         </is>
       </c>
-      <c r="D66" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage93.png</t>
-        </is>
+      <c r="D66" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image93.png")</f>
+        <v/>
       </c>
       <c r="E66" s="53" t="n"/>
       <c r="F66" s="54" t="n"/>
-      <c r="G66" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage94.png</t>
-        </is>
+      <c r="G66" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image94.png")</f>
+        <v/>
       </c>
       <c r="H66" s="42" t="n"/>
       <c r="I66" s="7" t="inlineStr">
@@ -2982,10 +2882,9 @@
           <t>1773371372804.png</t>
         </is>
       </c>
-      <c r="D67" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage95.png</t>
-        </is>
+      <c r="D67" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image95.png")</f>
+        <v/>
       </c>
       <c r="E67" s="57" t="n"/>
       <c r="F67" s="58" t="n"/>
@@ -3022,10 +2921,9 @@
       <c r="C69" s="17" t="n">
         <v>1773371662005</v>
       </c>
-      <c r="D69" s="45" t="inlineStr">
-        <is>
-          <t>replaced with urlimage96.png</t>
-        </is>
+      <c r="D69" s="45">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image96.png")</f>
+        <v/>
       </c>
       <c r="E69" s="45" t="n"/>
       <c r="F69" s="45" t="n"/>
@@ -3050,15 +2948,13 @@
       <c r="C70" s="18" t="n">
         <v>1773371662305</v>
       </c>
-      <c r="D70" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage97.png</t>
-        </is>
-      </c>
-      <c r="E70" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage98.png</t>
-        </is>
+      <c r="D70" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image97.png")</f>
+        <v/>
+      </c>
+      <c r="E70" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image98.png")</f>
+        <v/>
       </c>
       <c r="F70" s="56" t="n"/>
       <c r="G70" s="1" t="n"/>
@@ -3094,10 +2990,9 @@
       <c r="C72" s="55" t="n">
         <v>1773371663005</v>
       </c>
-      <c r="D72" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage99.png</t>
-        </is>
+      <c r="D72" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image99.png")</f>
+        <v/>
       </c>
       <c r="E72" s="56" t="n"/>
       <c r="F72" s="56" t="n"/>
@@ -3132,10 +3027,9 @@
       <c r="C74" s="16" t="n">
         <v>1773371663804</v>
       </c>
-      <c r="D74" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage100.png</t>
-        </is>
+      <c r="D74" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image100.png")</f>
+        <v/>
       </c>
       <c r="E74" s="42" t="n"/>
       <c r="F74" s="42" t="n"/>
@@ -3160,10 +3054,9 @@
       <c r="C75" s="16" t="n">
         <v>1773371664304</v>
       </c>
-      <c r="D75" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage101.png</t>
-        </is>
+      <c r="D75" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image101.png")</f>
+        <v/>
       </c>
       <c r="E75" s="42" t="n"/>
       <c r="F75" s="42" t="n"/>
@@ -3188,15 +3081,13 @@
       <c r="C76" s="18" t="n">
         <v>1773371665004</v>
       </c>
-      <c r="D76" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage102.png</t>
-        </is>
-      </c>
-      <c r="E76" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage103.png</t>
-        </is>
+      <c r="D76" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image102.png")</f>
+        <v/>
+      </c>
+      <c r="E76" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image103.png")</f>
+        <v/>
       </c>
       <c r="F76" s="56" t="n"/>
       <c r="G76" s="1" t="n"/>
@@ -3234,15 +3125,13 @@
           <t>1773371665204 - 1773371665605</t>
         </is>
       </c>
-      <c r="D78" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage104.png</t>
-        </is>
-      </c>
-      <c r="E78" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage105.png</t>
-        </is>
+      <c r="D78" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image104.png")</f>
+        <v/>
+      </c>
+      <c r="E78" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image105.png")</f>
+        <v/>
       </c>
       <c r="F78" s="42" t="n"/>
       <c r="G78" s="7" t="n"/>
@@ -3268,15 +3157,13 @@
           <t>1773371665805 - 1773371666105</t>
         </is>
       </c>
-      <c r="D79" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage106.png</t>
-        </is>
-      </c>
-      <c r="E79" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage107.png</t>
-        </is>
+      <c r="D79" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image106.png")</f>
+        <v/>
+      </c>
+      <c r="E79" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image107.png")</f>
+        <v/>
       </c>
       <c r="F79" s="42" t="n"/>
       <c r="G79" s="7" t="n"/>
@@ -3300,10 +3187,9 @@
       <c r="C80" s="16" t="n">
         <v>1773371666504</v>
       </c>
-      <c r="D80" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage108.png</t>
-        </is>
+      <c r="D80" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image108.png")</f>
+        <v/>
       </c>
       <c r="E80" s="42" t="n"/>
       <c r="F80" s="42" t="n"/>
@@ -3328,15 +3214,13 @@
       <c r="C81" s="18" t="n">
         <v>1773371672003</v>
       </c>
-      <c r="D81" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage109.png</t>
-        </is>
-      </c>
-      <c r="E81" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage110.png</t>
-        </is>
+      <c r="D81" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image109.png")</f>
+        <v/>
+      </c>
+      <c r="E81" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image110.png")</f>
+        <v/>
       </c>
       <c r="F81" s="56" t="n"/>
       <c r="G81" s="1" t="n"/>
@@ -3374,15 +3258,13 @@
           <t>1773371727505 - 1773371728604</t>
         </is>
       </c>
-      <c r="D83" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage111.png</t>
-        </is>
-      </c>
-      <c r="E83" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage112.png</t>
-        </is>
+      <c r="D83" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image111.png")</f>
+        <v/>
+      </c>
+      <c r="E83" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image112.png")</f>
+        <v/>
       </c>
       <c r="F83" s="56" t="n"/>
       <c r="G83" s="1" t="n"/>
@@ -3418,15 +3300,13 @@
           <t xml:space="preserve">1773371729704 - </t>
         </is>
       </c>
-      <c r="D85" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage113.png</t>
-        </is>
-      </c>
-      <c r="E85" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage114.png</t>
-        </is>
+      <c r="D85" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image113.png")</f>
+        <v/>
+      </c>
+      <c r="E85" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image114.png")</f>
+        <v/>
       </c>
       <c r="F85" s="56" t="n"/>
       <c r="G85" s="1" t="n"/>
@@ -3464,15 +3344,13 @@
           <t>1773371733604 - 1773371735704</t>
         </is>
       </c>
-      <c r="D87" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage115.png</t>
-        </is>
-      </c>
-      <c r="E87" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage116.png</t>
-        </is>
+      <c r="D87" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image115.png")</f>
+        <v/>
+      </c>
+      <c r="E87" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image116.png")</f>
+        <v/>
       </c>
       <c r="F87" s="42" t="n"/>
       <c r="G87" s="7" t="n"/>
@@ -3498,15 +3376,13 @@
           <t>1773371734705 - 1773371735605</t>
         </is>
       </c>
-      <c r="D88" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage117.png</t>
-        </is>
-      </c>
-      <c r="E88" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage118.png</t>
-        </is>
+      <c r="D88" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image117.png")</f>
+        <v/>
+      </c>
+      <c r="E88" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image118.png")</f>
+        <v/>
       </c>
       <c r="F88" s="42" t="n"/>
       <c r="G88" s="7" t="n"/>
@@ -3532,15 +3408,13 @@
           <t>1773371742605 - 1773371743704</t>
         </is>
       </c>
-      <c r="D89" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage119.png</t>
-        </is>
-      </c>
-      <c r="E89" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage120.png</t>
-        </is>
+      <c r="D89" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image119.png")</f>
+        <v/>
+      </c>
+      <c r="E89" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image120.png")</f>
+        <v/>
       </c>
       <c r="F89" s="42" t="n"/>
       <c r="G89" s="7" t="n"/>
@@ -3566,15 +3440,13 @@
           <t>1773371743005 - 1773371744704</t>
         </is>
       </c>
-      <c r="D90" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage121.png</t>
-        </is>
-      </c>
-      <c r="E90" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage122.png</t>
-        </is>
+      <c r="D90" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image121.png")</f>
+        <v/>
+      </c>
+      <c r="E90" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image122.png")</f>
+        <v/>
       </c>
       <c r="F90" s="42" t="n"/>
       <c r="G90" s="7" t="n"/>
@@ -3600,15 +3472,13 @@
           <t xml:space="preserve">1773371748905 - 1773371749605 </t>
         </is>
       </c>
-      <c r="D91" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage123.png</t>
-        </is>
-      </c>
-      <c r="E91" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage124.png</t>
-        </is>
+      <c r="D91" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image123.png")</f>
+        <v/>
+      </c>
+      <c r="E91" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image124.png")</f>
+        <v/>
       </c>
       <c r="F91" s="56" t="n"/>
       <c r="G91" s="1" t="n"/>
@@ -3642,10 +3512,9 @@
       <c r="C93" s="16" t="n">
         <v>1773371751204</v>
       </c>
-      <c r="D93" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage125.png</t>
-        </is>
+      <c r="D93" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image125.png")</f>
+        <v/>
       </c>
       <c r="E93" s="42" t="n"/>
       <c r="F93" s="42" t="n"/>
@@ -3670,20 +3539,17 @@
       <c r="C94" s="18" t="n">
         <v>1773371766904</v>
       </c>
-      <c r="D94" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage126.png</t>
-        </is>
-      </c>
-      <c r="E94" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage127.png</t>
-        </is>
-      </c>
-      <c r="F94" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage128.png</t>
-        </is>
+      <c r="D94" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image126.png")</f>
+        <v/>
+      </c>
+      <c r="E94" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image127.png")</f>
+        <v/>
+      </c>
+      <c r="F94" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image128.png")</f>
+        <v/>
       </c>
       <c r="G94" s="1" t="n"/>
       <c r="I94" s="1" t="inlineStr">
@@ -3744,15 +3610,13 @@
       <c r="C98" s="18" t="n">
         <v>1773371768505</v>
       </c>
-      <c r="D98" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage129.png</t>
-        </is>
-      </c>
-      <c r="E98" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage130.png</t>
-        </is>
+      <c r="D98" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image129.png")</f>
+        <v/>
+      </c>
+      <c r="E98" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image130.png")</f>
+        <v/>
       </c>
       <c r="F98" s="56" t="n"/>
       <c r="G98" s="5" t="n"/>
@@ -3850,10 +3714,9 @@
       <c r="C105" s="18" t="n">
         <v>1773371769804</v>
       </c>
-      <c r="D105" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage131.png</t>
-        </is>
+      <c r="D105" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image131.png")</f>
+        <v/>
       </c>
       <c r="E105" s="56" t="n"/>
       <c r="F105" s="56" t="n"/>
@@ -3898,15 +3761,13 @@
           <t>1773371785504 - 1773371788604</t>
         </is>
       </c>
-      <c r="D107" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage132.png</t>
-        </is>
-      </c>
-      <c r="E107" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage133.png</t>
-        </is>
+      <c r="D107" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image132.png")</f>
+        <v/>
+      </c>
+      <c r="E107" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image133.png")</f>
+        <v/>
       </c>
       <c r="F107" s="42" t="n"/>
       <c r="G107" s="7" t="n"/>
@@ -3932,15 +3793,13 @@
           <t xml:space="preserve">1773371788704 - </t>
         </is>
       </c>
-      <c r="D108" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage134.png</t>
-        </is>
-      </c>
-      <c r="E108" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage135.png</t>
-        </is>
+      <c r="D108" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image134.png")</f>
+        <v/>
+      </c>
+      <c r="E108" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image135.png")</f>
+        <v/>
       </c>
       <c r="F108" s="56" t="n"/>
       <c r="G108" s="1" t="n"/>
@@ -3978,15 +3837,13 @@
           <t>1773371789905 - 1773371790904</t>
         </is>
       </c>
-      <c r="D110" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage136.png</t>
-        </is>
-      </c>
-      <c r="E110" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage137.png</t>
-        </is>
+      <c r="D110" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image136.png")</f>
+        <v/>
+      </c>
+      <c r="E110" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image137.png")</f>
+        <v/>
       </c>
       <c r="F110" s="56" t="n"/>
       <c r="G110" s="1" t="n"/>
@@ -4022,15 +3879,13 @@
           <t>1773371791005 - 1773371791904</t>
         </is>
       </c>
-      <c r="D112" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage138.png</t>
-        </is>
-      </c>
-      <c r="E112" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage139.png</t>
-        </is>
+      <c r="D112" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image138.png")</f>
+        <v/>
+      </c>
+      <c r="E112" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image139.png")</f>
+        <v/>
       </c>
       <c r="F112" s="56" t="n"/>
       <c r="G112" s="1" t="n"/>
@@ -4066,15 +3921,13 @@
           <t xml:space="preserve">1773371792104 - </t>
         </is>
       </c>
-      <c r="D114" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage140.png</t>
-        </is>
-      </c>
-      <c r="E114" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage141.png</t>
-        </is>
+      <c r="D114" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image140.png")</f>
+        <v/>
+      </c>
+      <c r="E114" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image141.png")</f>
+        <v/>
       </c>
       <c r="F114" s="56" t="n"/>
       <c r="G114" s="1" t="n"/>
@@ -4112,15 +3965,13 @@
           <t xml:space="preserve">1773371796104 - </t>
         </is>
       </c>
-      <c r="D116" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage142.png</t>
-        </is>
-      </c>
-      <c r="E116" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage143.png</t>
-        </is>
+      <c r="D116" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image142.png")</f>
+        <v/>
+      </c>
+      <c r="E116" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image143.png")</f>
+        <v/>
       </c>
       <c r="F116" s="56" t="n"/>
       <c r="G116" s="1" t="n"/>
@@ -4158,15 +4009,13 @@
           <t xml:space="preserve">1773371798904 - </t>
         </is>
       </c>
-      <c r="D118" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage144.png</t>
-        </is>
-      </c>
-      <c r="E118" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage145.png</t>
-        </is>
+      <c r="D118" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image144.png")</f>
+        <v/>
+      </c>
+      <c r="E118" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image145.png")</f>
+        <v/>
       </c>
       <c r="F118" s="56" t="n"/>
       <c r="G118" s="1" t="n"/>
@@ -4204,15 +4053,13 @@
           <t>1773371800905 - 1773371802804</t>
         </is>
       </c>
-      <c r="D120" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage146.png</t>
-        </is>
-      </c>
-      <c r="E120" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage147.png</t>
-        </is>
+      <c r="D120" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image146.png")</f>
+        <v/>
+      </c>
+      <c r="E120" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image147.png")</f>
+        <v/>
       </c>
       <c r="F120" s="42" t="n"/>
       <c r="G120" s="7" t="n"/>
@@ -4238,15 +4085,13 @@
           <t xml:space="preserve">1773371803704 - </t>
         </is>
       </c>
-      <c r="D121" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage148.png</t>
-        </is>
-      </c>
-      <c r="E121" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage149.png</t>
-        </is>
+      <c r="D121" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image148.png")</f>
+        <v/>
+      </c>
+      <c r="E121" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image149.png")</f>
+        <v/>
       </c>
       <c r="F121" s="56" t="n"/>
       <c r="G121" s="1" t="n"/>
@@ -4284,10 +4129,9 @@
           <t>1773371807304 - 1773371809005</t>
         </is>
       </c>
-      <c r="D123" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage150.png</t>
-        </is>
+      <c r="D123" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image150.png")</f>
+        <v/>
       </c>
       <c r="E123" s="42" t="n"/>
       <c r="F123" s="42" t="n"/>
@@ -4314,10 +4158,9 @@
           <t>1773371810005 - 1773371810904</t>
         </is>
       </c>
-      <c r="D124" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage151.png</t>
-        </is>
+      <c r="D124" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image151.png")</f>
+        <v/>
       </c>
       <c r="E124" s="42" t="n"/>
       <c r="F124" s="42" t="n"/>
@@ -4344,15 +4187,13 @@
           <t xml:space="preserve">1773371827505 - </t>
         </is>
       </c>
-      <c r="D125" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage152.png</t>
-        </is>
-      </c>
-      <c r="E125" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage153.png</t>
-        </is>
+      <c r="D125" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image152.png")</f>
+        <v/>
+      </c>
+      <c r="E125" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image153.png")</f>
+        <v/>
       </c>
       <c r="F125" s="56" t="n"/>
       <c r="G125" s="1" t="n"/>
@@ -4390,15 +4231,13 @@
           <t xml:space="preserve">1773371830104 - </t>
         </is>
       </c>
-      <c r="D127" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage154.png</t>
-        </is>
-      </c>
-      <c r="E127" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage155.png</t>
-        </is>
+      <c r="D127" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image154.png")</f>
+        <v/>
+      </c>
+      <c r="E127" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image155.png")</f>
+        <v/>
       </c>
       <c r="F127" s="56" t="n"/>
       <c r="G127" s="1" t="n"/>
@@ -4436,15 +4275,13 @@
           <t xml:space="preserve">1773371831005 - </t>
         </is>
       </c>
-      <c r="D129" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage156.png</t>
-        </is>
-      </c>
-      <c r="E129" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage157.png</t>
-        </is>
+      <c r="D129" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image156.png")</f>
+        <v/>
+      </c>
+      <c r="E129" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image157.png")</f>
+        <v/>
       </c>
       <c r="F129" s="56" t="n"/>
       <c r="G129" s="1" t="n"/>
@@ -4482,15 +4319,13 @@
           <t>1773371833204 - 1773371834105</t>
         </is>
       </c>
-      <c r="D131" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage158.png</t>
-        </is>
-      </c>
-      <c r="E131" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage159.png</t>
-        </is>
+      <c r="D131" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image158.png")</f>
+        <v/>
+      </c>
+      <c r="E131" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image159.png")</f>
+        <v/>
       </c>
       <c r="F131" s="42" t="n"/>
       <c r="G131" s="7" t="n"/>
@@ -4516,15 +4351,13 @@
           <t xml:space="preserve">1773371837204 - </t>
         </is>
       </c>
-      <c r="D132" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage160.png</t>
-        </is>
-      </c>
-      <c r="E132" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage161.png</t>
-        </is>
+      <c r="D132" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image160.png")</f>
+        <v/>
+      </c>
+      <c r="E132" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image161.png")</f>
+        <v/>
       </c>
       <c r="F132" s="56" t="n"/>
       <c r="G132" s="1" t="n"/>
@@ -4562,15 +4395,13 @@
           <t xml:space="preserve">1773371872804 - </t>
         </is>
       </c>
-      <c r="D134" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage162.png</t>
-        </is>
-      </c>
-      <c r="E134" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage163.png</t>
-        </is>
+      <c r="D134" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image162.png")</f>
+        <v/>
+      </c>
+      <c r="E134" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image163.png")</f>
+        <v/>
       </c>
       <c r="F134" s="56" t="n"/>
       <c r="G134" s="1" t="n"/>
@@ -4608,15 +4439,13 @@
           <t xml:space="preserve">1773371885104 - </t>
         </is>
       </c>
-      <c r="D136" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage164.png</t>
-        </is>
-      </c>
-      <c r="E136" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage165.png</t>
-        </is>
+      <c r="D136" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image164.png")</f>
+        <v/>
+      </c>
+      <c r="E136" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image165.png")</f>
+        <v/>
       </c>
       <c r="F136" s="56" t="n"/>
       <c r="G136" s="1" t="n"/>
@@ -4654,15 +4483,13 @@
           <t xml:space="preserve">1773371893305 - </t>
         </is>
       </c>
-      <c r="D138" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage166.png</t>
-        </is>
-      </c>
-      <c r="E138" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage167.png</t>
-        </is>
+      <c r="D138" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image166.png")</f>
+        <v/>
+      </c>
+      <c r="E138" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image167.png")</f>
+        <v/>
       </c>
       <c r="F138" s="56" t="n"/>
       <c r="G138" s="1" t="n"/>
@@ -4700,15 +4527,13 @@
           <t>1773371900605 - 1773371901704</t>
         </is>
       </c>
-      <c r="D140" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage168.png</t>
-        </is>
-      </c>
-      <c r="E140" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage169.png</t>
-        </is>
+      <c r="D140" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image168.png")</f>
+        <v/>
+      </c>
+      <c r="E140" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image169.png")</f>
+        <v/>
       </c>
       <c r="F140" s="42" t="n"/>
       <c r="G140" s="7" t="n"/>
@@ -4734,15 +4559,13 @@
           <t xml:space="preserve">1773371901604 - </t>
         </is>
       </c>
-      <c r="D141" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage170.png</t>
-        </is>
-      </c>
-      <c r="E141" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage171.png</t>
-        </is>
+      <c r="D141" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image170.png")</f>
+        <v/>
+      </c>
+      <c r="E141" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image171.png")</f>
+        <v/>
       </c>
       <c r="F141" s="56" t="n"/>
       <c r="G141" s="1" t="n"/>
@@ -4780,15 +4603,13 @@
           <t xml:space="preserve">1773371916304 - </t>
         </is>
       </c>
-      <c r="D143" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage172.png</t>
-        </is>
-      </c>
-      <c r="E143" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage173.png</t>
-        </is>
+      <c r="D143" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image172.png")</f>
+        <v/>
+      </c>
+      <c r="E143" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image173.png")</f>
+        <v/>
       </c>
       <c r="F143" s="56" t="n"/>
       <c r="G143" s="1" t="n"/>
@@ -4826,15 +4647,13 @@
           <t>1773371918204 - 1773371919105</t>
         </is>
       </c>
-      <c r="D145" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage174.png</t>
-        </is>
-      </c>
-      <c r="E145" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage175.png</t>
-        </is>
+      <c r="D145" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image174.png")</f>
+        <v/>
+      </c>
+      <c r="E145" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image175.png")</f>
+        <v/>
       </c>
       <c r="F145" s="42" t="n"/>
       <c r="G145" s="7" t="n"/>
@@ -4860,15 +4679,13 @@
           <t>1773371919205 - 1773371920005</t>
         </is>
       </c>
-      <c r="D146" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage176.png</t>
-        </is>
-      </c>
-      <c r="E146" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage177.png</t>
-        </is>
+      <c r="D146" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image176.png")</f>
+        <v/>
+      </c>
+      <c r="E146" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image177.png")</f>
+        <v/>
       </c>
       <c r="F146" s="42" t="n"/>
       <c r="G146" s="7" t="n"/>
@@ -4894,15 +4711,13 @@
           <t>1773371924604 - 1773371925004</t>
         </is>
       </c>
-      <c r="D147" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage178.png</t>
-        </is>
-      </c>
-      <c r="E147" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage179.png</t>
-        </is>
+      <c r="D147" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image178.png")</f>
+        <v/>
+      </c>
+      <c r="E147" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image179.png")</f>
+        <v/>
       </c>
       <c r="F147" s="42" t="n"/>
       <c r="G147" s="7" t="n"/>
@@ -4928,15 +4743,13 @@
           <t xml:space="preserve">1773371926105 - </t>
         </is>
       </c>
-      <c r="D148" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage180.png</t>
-        </is>
-      </c>
-      <c r="E148" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage181.png</t>
-        </is>
+      <c r="D148" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image180.png")</f>
+        <v/>
+      </c>
+      <c r="E148" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image181.png")</f>
+        <v/>
       </c>
       <c r="F148" s="56" t="n"/>
       <c r="G148" s="1" t="n"/>
@@ -4974,15 +4787,13 @@
           <t>1773371928104 - 1773371929004</t>
         </is>
       </c>
-      <c r="D150" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage182.png</t>
-        </is>
-      </c>
-      <c r="E150" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage182.png</t>
-        </is>
+      <c r="D150" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image182.png")</f>
+        <v/>
+      </c>
+      <c r="E150" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image182.png")</f>
+        <v/>
       </c>
       <c r="F150" s="56" t="n"/>
       <c r="G150" s="1" t="n"/>
@@ -5018,15 +4829,13 @@
           <t xml:space="preserve">1773371930305 - </t>
         </is>
       </c>
-      <c r="D152" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage183.png</t>
-        </is>
-      </c>
-      <c r="E152" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage184.png</t>
-        </is>
+      <c r="D152" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image183.png")</f>
+        <v/>
+      </c>
+      <c r="E152" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image184.png")</f>
+        <v/>
       </c>
       <c r="F152" s="56" t="n"/>
       <c r="G152" s="1" t="n"/>
@@ -5062,15 +4871,13 @@
       <c r="C154" s="18" t="n">
         <v>1773371937704</v>
       </c>
-      <c r="D154" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage185.png</t>
-        </is>
-      </c>
-      <c r="E154" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage186.png</t>
-        </is>
+      <c r="D154" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image185.png")</f>
+        <v/>
+      </c>
+      <c r="E154" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image186.png")</f>
+        <v/>
       </c>
       <c r="F154" s="56" t="n"/>
       <c r="G154" s="1" t="n"/>
@@ -5108,15 +4915,13 @@
           <t>1773371938304 - 1773371939304</t>
         </is>
       </c>
-      <c r="D156" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage187.png</t>
-        </is>
-      </c>
-      <c r="E156" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage188.png</t>
-        </is>
+      <c r="D156" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image187.png")</f>
+        <v/>
+      </c>
+      <c r="E156" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image188.png")</f>
+        <v/>
       </c>
       <c r="F156" s="56" t="n"/>
       <c r="G156" s="1" t="n"/>
@@ -5152,15 +4957,13 @@
           <t>1773371993504 - 1773371994104</t>
         </is>
       </c>
-      <c r="D158" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage189.png</t>
-        </is>
-      </c>
-      <c r="E158" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage190.png</t>
-        </is>
+      <c r="D158" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image189.png")</f>
+        <v/>
+      </c>
+      <c r="E158" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image190.png")</f>
+        <v/>
       </c>
       <c r="F158" s="42" t="n"/>
       <c r="G158" s="7" t="n"/>
@@ -5186,15 +4989,13 @@
           <t xml:space="preserve">1773371993504 - </t>
         </is>
       </c>
-      <c r="D159" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage189.png</t>
-        </is>
-      </c>
-      <c r="E159" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage191.png</t>
-        </is>
+      <c r="D159" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image189.png")</f>
+        <v/>
+      </c>
+      <c r="E159" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image191.png")</f>
+        <v/>
       </c>
       <c r="F159" s="56" t="n"/>
       <c r="G159" s="1" t="n"/>
@@ -5232,15 +5033,13 @@
           <t>1773371993504 - 1773371996005</t>
         </is>
       </c>
-      <c r="D161" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage189.png</t>
-        </is>
-      </c>
-      <c r="E161" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage192.png</t>
-        </is>
+      <c r="D161" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image189.png")</f>
+        <v/>
+      </c>
+      <c r="E161" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image192.png")</f>
+        <v/>
       </c>
       <c r="F161" s="56" t="n"/>
       <c r="G161" s="3" t="n"/>
@@ -5290,15 +5089,13 @@
           <t xml:space="preserve">1773371995505 - </t>
         </is>
       </c>
-      <c r="D164" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage193.png</t>
-        </is>
-      </c>
-      <c r="E164" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage194.png</t>
-        </is>
+      <c r="D164" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image193.png")</f>
+        <v/>
+      </c>
+      <c r="E164" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image194.png")</f>
+        <v/>
       </c>
       <c r="F164" s="56" t="n"/>
       <c r="G164" s="1" t="n"/>
@@ -5334,10 +5131,9 @@
       <c r="C166" s="16" t="n">
         <v>1773372003005</v>
       </c>
-      <c r="D166" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage195.png</t>
-        </is>
+      <c r="D166" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image195.png")</f>
+        <v/>
       </c>
       <c r="E166" s="42" t="n"/>
       <c r="F166" s="42" t="n"/>
@@ -5362,10 +5158,9 @@
       <c r="C167" s="17" t="n">
         <v>1773372005805</v>
       </c>
-      <c r="D167" s="45" t="inlineStr">
-        <is>
-          <t>replaced with urlimage196.png</t>
-        </is>
+      <c r="D167" s="45">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image196.png")</f>
+        <v/>
       </c>
       <c r="E167" s="45" t="n"/>
       <c r="F167" s="45" t="n"/>
@@ -5392,10 +5187,9 @@
           <t>1773372005705_1773372005604</t>
         </is>
       </c>
-      <c r="D168" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage197.png</t>
-        </is>
+      <c r="D168" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image197.png")</f>
+        <v/>
       </c>
       <c r="E168" s="42" t="n"/>
       <c r="F168" s="42" t="n"/>
@@ -5422,10 +5216,9 @@
           <t>1773372011604_1773372011704,1773372012404,1773372012304,1773372012204,1773372012104,</t>
         </is>
       </c>
-      <c r="D169" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage198.png</t>
-        </is>
+      <c r="D169" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image198.png")</f>
+        <v/>
       </c>
       <c r="E169" s="42" t="n"/>
       <c r="F169" s="42" t="n"/>
@@ -5450,10 +5243,9 @@
       <c r="C170" s="16" t="n">
         <v>1.77337204660517e+25</v>
       </c>
-      <c r="D170" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage199.png</t>
-        </is>
+      <c r="D170" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image199.png")</f>
+        <v/>
       </c>
       <c r="E170" s="42" t="n"/>
       <c r="F170" s="42" t="n"/>
@@ -5480,10 +5272,9 @@
           <t xml:space="preserve">1773372048804, 1773372048604_1773372049504,1773372065505, </t>
         </is>
       </c>
-      <c r="D171" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage200.png</t>
-        </is>
+      <c r="D171" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image200.png")</f>
+        <v/>
       </c>
       <c r="E171" s="56" t="n"/>
       <c r="F171" s="56" t="n"/>
@@ -5538,10 +5329,9 @@
           <t>1773372080005_1773372080505</t>
         </is>
       </c>
-      <c r="D174" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage201.png</t>
-        </is>
+      <c r="D174" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image201.png")</f>
+        <v/>
       </c>
       <c r="E174" s="42" t="n"/>
       <c r="F174" s="42" t="n"/>
@@ -5568,10 +5358,9 @@
           <t>1773372083904_1773372083805</t>
         </is>
       </c>
-      <c r="D175" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage202.png</t>
-        </is>
+      <c r="D175" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image202.png")</f>
+        <v/>
       </c>
       <c r="E175" s="42" t="n"/>
       <c r="F175" s="42" t="n"/>
@@ -5598,10 +5387,9 @@
           <t>1773372083004_1773372084205</t>
         </is>
       </c>
-      <c r="D176" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage203.png</t>
-        </is>
+      <c r="D176" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image203.png")</f>
+        <v/>
       </c>
       <c r="E176" s="42" t="n"/>
       <c r="F176" s="42" t="n"/>
@@ -5628,10 +5416,9 @@
           <t>1773372095704_1773372096304</t>
         </is>
       </c>
-      <c r="D177" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage204.png</t>
-        </is>
+      <c r="D177" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image204.png")</f>
+        <v/>
       </c>
       <c r="E177" s="56" t="n"/>
       <c r="F177" s="56" t="n"/>
@@ -5672,10 +5459,9 @@
           <t>1773372109305,1773372109605,1773372109505,1773372110504,</t>
         </is>
       </c>
-      <c r="D179" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage205.png</t>
-        </is>
+      <c r="D179" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image205.png")</f>
+        <v/>
       </c>
       <c r="E179" s="42" t="n"/>
       <c r="F179" s="42" t="n"/>
@@ -5700,10 +5486,9 @@
       <c r="C180" s="16" t="n">
         <v>1773372122304</v>
       </c>
-      <c r="D180" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage206.png</t>
-        </is>
+      <c r="D180" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image206.png")</f>
+        <v/>
       </c>
       <c r="E180" s="42" t="n"/>
       <c r="F180" s="42" t="n"/>
@@ -5730,10 +5515,9 @@
           <t>1773372131804,</t>
         </is>
       </c>
-      <c r="D181" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage207.png</t>
-        </is>
+      <c r="D181" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image207.png")</f>
+        <v/>
       </c>
       <c r="E181" s="56" t="n"/>
       <c r="F181" s="56" t="n"/>
@@ -5770,10 +5554,9 @@
           <t>177372132404_1773372133304</t>
         </is>
       </c>
-      <c r="D183" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage208.png</t>
-        </is>
+      <c r="D183" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image208.png")</f>
+        <v/>
       </c>
       <c r="E183" s="42" t="n"/>
       <c r="F183" s="42" t="n"/>
@@ -5800,10 +5583,9 @@
           <t>1773372143704_1773372153504</t>
         </is>
       </c>
-      <c r="D184" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage209.png</t>
-        </is>
+      <c r="D184" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image209.png")</f>
+        <v/>
       </c>
       <c r="E184" s="42" t="n"/>
       <c r="F184" s="42" t="n"/>
@@ -5830,10 +5612,9 @@
           <t>1773372161105_1773372162005</t>
         </is>
       </c>
-      <c r="D185" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage210.png</t>
-        </is>
+      <c r="D185" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image210.png")</f>
+        <v/>
       </c>
       <c r="E185" s="42" t="n"/>
       <c r="F185" s="42" t="n"/>
@@ -5860,10 +5641,9 @@
           <t>1773372163805_1773372164704</t>
         </is>
       </c>
-      <c r="D186" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage211.png</t>
-        </is>
+      <c r="D186" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image211.png")</f>
+        <v/>
       </c>
       <c r="E186" s="42" t="n"/>
       <c r="F186" s="42" t="n"/>
@@ -5890,10 +5670,9 @@
           <t>1773372183904,1773372184005,1773372183804,</t>
         </is>
       </c>
-      <c r="D187" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage212.png</t>
-        </is>
+      <c r="D187" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image212.png")</f>
+        <v/>
       </c>
       <c r="E187" s="56" t="n"/>
       <c r="F187" s="56" t="n"/>
@@ -5930,10 +5709,9 @@
           <t>1773372225004,1773372225104,17733722240904,</t>
         </is>
       </c>
-      <c r="D189" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage213.png</t>
-        </is>
+      <c r="D189" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image213.png")</f>
+        <v/>
       </c>
       <c r="E189" s="42" t="n"/>
       <c r="F189" s="42" t="n"/>
@@ -5960,10 +5738,9 @@
           <t>1773372248004_1773372248805</t>
         </is>
       </c>
-      <c r="D190" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage214.png</t>
-        </is>
+      <c r="D190" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image214.png")</f>
+        <v/>
       </c>
       <c r="E190" s="56" t="n"/>
       <c r="F190" s="56" t="n"/>
@@ -6004,10 +5781,9 @@
           <t>1773372249105_1773372249305</t>
         </is>
       </c>
-      <c r="D192" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage215.png</t>
-        </is>
+      <c r="D192" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image215.png")</f>
+        <v/>
       </c>
       <c r="E192" s="42" t="n"/>
       <c r="F192" s="42" t="n"/>
@@ -6034,10 +5810,9 @@
           <t>1773372268104,1773372261604,1773372261504,1773372261704,1773372262705,</t>
         </is>
       </c>
-      <c r="D193" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage216.png</t>
-        </is>
+      <c r="D193" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image216.png")</f>
+        <v/>
       </c>
       <c r="E193" s="42" t="n"/>
       <c r="F193" s="42" t="n"/>
@@ -6062,10 +5837,9 @@
       <c r="C194" s="16" t="n">
         <v>1773372347705</v>
       </c>
-      <c r="D194" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage217.png</t>
-        </is>
+      <c r="D194" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image217.png")</f>
+        <v/>
       </c>
       <c r="E194" s="42" t="n"/>
       <c r="F194" s="42" t="n"/>
@@ -6090,15 +5864,13 @@
       <c r="C195" s="17" t="n">
         <v>1773371376904</v>
       </c>
-      <c r="D195" s="24" t="inlineStr">
-        <is>
-          <t>replaced with urlimage218.png</t>
-        </is>
-      </c>
-      <c r="E195" s="24" t="inlineStr">
-        <is>
-          <t>replaced with urlimage219.png</t>
-        </is>
+      <c r="D195" s="24">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image218.png")</f>
+        <v/>
+      </c>
+      <c r="E195" s="24">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image219.png")</f>
+        <v/>
       </c>
       <c r="F195" s="45" t="n"/>
       <c r="G195" s="2" t="n"/>
@@ -6124,15 +5896,13 @@
           <t>1773371377304 - 1773371378204</t>
         </is>
       </c>
-      <c r="D196" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage220.png</t>
-        </is>
-      </c>
-      <c r="E196" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage221.png</t>
-        </is>
+      <c r="D196" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image220.png")</f>
+        <v/>
+      </c>
+      <c r="E196" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image221.png")</f>
+        <v/>
       </c>
       <c r="F196" s="56" t="n"/>
       <c r="G196" s="1" t="n"/>
@@ -6168,15 +5938,13 @@
           <t>1773371381504 - 1773371382505</t>
         </is>
       </c>
-      <c r="D198" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage222.png</t>
-        </is>
-      </c>
-      <c r="E198" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage223.png</t>
-        </is>
+      <c r="D198" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image222.png")</f>
+        <v/>
+      </c>
+      <c r="E198" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image223.png")</f>
+        <v/>
       </c>
       <c r="F198" s="42" t="n"/>
       <c r="G198" s="7" t="n"/>
@@ -6202,15 +5970,13 @@
           <t>1773371383704 - 1773371390904, 1773371392104 - 1773371394904, 1773371395105, 1773371398604 - 1773371399504, 1773371400705 - 1773371403804, 1773371407104 - 1773371408705, 1773371410005 - 1773371411004, 1773371414304 - 1773371415204</t>
         </is>
       </c>
-      <c r="D199" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage224.png</t>
-        </is>
-      </c>
-      <c r="E199" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage225.png</t>
-        </is>
+      <c r="D199" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image224.png")</f>
+        <v/>
+      </c>
+      <c r="E199" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image225.png")</f>
+        <v/>
       </c>
       <c r="F199" s="56" t="n"/>
       <c r="G199" s="1" t="n"/>
@@ -6246,15 +6012,13 @@
           <t>1773371421604 - 1773371422604</t>
         </is>
       </c>
-      <c r="D201" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage226.png</t>
-        </is>
-      </c>
-      <c r="E201" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage227.png</t>
-        </is>
+      <c r="D201" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image226.png")</f>
+        <v/>
+      </c>
+      <c r="E201" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image227.png")</f>
+        <v/>
       </c>
       <c r="F201" s="42" t="n"/>
       <c r="G201" s="7" t="n"/>
@@ -6280,15 +6044,13 @@
           <t>1773371422705 - 1773371423705, 1773371427004 - 1773371427904</t>
         </is>
       </c>
-      <c r="D202" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage228.png</t>
-        </is>
-      </c>
-      <c r="E202" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage229.png</t>
-        </is>
+      <c r="D202" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image228.png")</f>
+        <v/>
+      </c>
+      <c r="E202" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image229.png")</f>
+        <v/>
       </c>
       <c r="F202" s="56" t="n"/>
       <c r="G202" s="1" t="n"/>
@@ -6324,15 +6086,13 @@
           <t>1773371434000, 1773371434703, 1773371434903, 1773371435303, 1773371435503, 1773371437803, 1773371438403, 1773371438703, 1773371440700, 1773371441200, 1773371441903, 1773371442503, 1773371443503, 1773371443803, 1773371444103, 1773371445000, 1773371446100, 1773371446700</t>
         </is>
       </c>
-      <c r="D204" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage230.png</t>
-        </is>
-      </c>
-      <c r="E204" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage231.png</t>
-        </is>
+      <c r="D204" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image230.png")</f>
+        <v/>
+      </c>
+      <c r="E204" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image231.png")</f>
+        <v/>
       </c>
       <c r="F204" s="42" t="n"/>
       <c r="G204" s="7" t="n"/>
@@ -6356,15 +6116,13 @@
       <c r="C205" s="16" t="n">
         <v>1773371446804</v>
       </c>
-      <c r="D205" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage232.png</t>
-        </is>
-      </c>
-      <c r="E205" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage233.png</t>
-        </is>
+      <c r="D205" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image232.png")</f>
+        <v/>
+      </c>
+      <c r="E205" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image233.png")</f>
+        <v/>
       </c>
       <c r="F205" s="42" t="n"/>
       <c r="G205" s="7" t="n"/>
@@ -6390,15 +6148,13 @@
           <t xml:space="preserve">1773371447503, </t>
         </is>
       </c>
-      <c r="D206" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage234.png</t>
-        </is>
-      </c>
-      <c r="E206" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage235.png</t>
-        </is>
+      <c r="D206" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image234.png")</f>
+        <v/>
+      </c>
+      <c r="E206" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image235.png")</f>
+        <v/>
       </c>
       <c r="F206" s="56" t="n"/>
       <c r="G206" s="1" t="n"/>
@@ -6432,15 +6188,13 @@
       <c r="C208" s="16" t="n">
         <v>1773371447905</v>
       </c>
-      <c r="D208" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage236.png</t>
-        </is>
-      </c>
-      <c r="E208" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage237.png</t>
-        </is>
+      <c r="D208" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image236.png")</f>
+        <v/>
+      </c>
+      <c r="E208" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image237.png")</f>
+        <v/>
       </c>
       <c r="F208" s="42" t="n"/>
       <c r="G208" s="7" t="n"/>
@@ -6466,20 +6220,17 @@
           <t>1773371448103, 1773371449700, 1773371449804, 1773371450903, 1773371451203, 1773371451703</t>
         </is>
       </c>
-      <c r="D209" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage238.png</t>
-        </is>
-      </c>
-      <c r="E209" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage239.png</t>
-        </is>
-      </c>
-      <c r="F209" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage240.png</t>
-        </is>
+      <c r="D209" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image238.png")</f>
+        <v/>
+      </c>
+      <c r="E209" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image239.png")</f>
+        <v/>
+      </c>
+      <c r="F209" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image240.png")</f>
+        <v/>
       </c>
       <c r="G209" s="1" t="n"/>
       <c r="I209" s="1" t="inlineStr">
@@ -6514,15 +6265,13 @@
           <t>1773371451905 - 1773371452805</t>
         </is>
       </c>
-      <c r="D211" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage241.png</t>
-        </is>
-      </c>
-      <c r="E211" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage242.png</t>
-        </is>
+      <c r="D211" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image241.png")</f>
+        <v/>
+      </c>
+      <c r="E211" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image242.png")</f>
+        <v/>
       </c>
       <c r="F211" s="42" t="n"/>
       <c r="G211" s="7" t="n"/>
@@ -6548,15 +6297,13 @@
           <t>1773371455705 - 1773371456605</t>
         </is>
       </c>
-      <c r="D212" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage243.png</t>
-        </is>
-      </c>
-      <c r="E212" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage244.png</t>
-        </is>
+      <c r="D212" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image243.png")</f>
+        <v/>
+      </c>
+      <c r="E212" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image244.png")</f>
+        <v/>
       </c>
       <c r="F212" s="42" t="n"/>
       <c r="G212" s="7" t="n"/>
@@ -6582,15 +6329,13 @@
           <t>1773371457904 - 1773371458905</t>
         </is>
       </c>
-      <c r="D213" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage245.png</t>
-        </is>
-      </c>
-      <c r="E213" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage246.png</t>
-        </is>
+      <c r="D213" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image245.png")</f>
+        <v/>
+      </c>
+      <c r="E213" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image246.png")</f>
+        <v/>
       </c>
       <c r="F213" s="42" t="n"/>
       <c r="G213" s="7" t="n"/>
@@ -6616,15 +6361,13 @@
           <t>1773371461105 - 1773371462004, 1773371463204, 1773371463304, 1773371463505, 1773371463605, 1773371463905 - 1773371464205</t>
         </is>
       </c>
-      <c r="D214" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage247.png</t>
-        </is>
-      </c>
-      <c r="E214" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage248.png</t>
-        </is>
+      <c r="D214" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image247.png")</f>
+        <v/>
+      </c>
+      <c r="E214" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image248.png")</f>
+        <v/>
       </c>
       <c r="F214" s="42" t="n"/>
       <c r="G214" s="7" t="n"/>
@@ -6650,15 +6393,13 @@
           <t>1773371471505 - 1773371473905</t>
         </is>
       </c>
-      <c r="D215" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage249.png</t>
-        </is>
-      </c>
-      <c r="E215" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage250.png</t>
-        </is>
+      <c r="D215" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image249.png")</f>
+        <v/>
+      </c>
+      <c r="E215" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image250.png")</f>
+        <v/>
       </c>
       <c r="F215" s="42" t="n"/>
       <c r="G215" s="7" t="n"/>
@@ -6684,15 +6425,13 @@
           <t>1773371475604, 1773371476005</t>
         </is>
       </c>
-      <c r="D216" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage251.png</t>
-        </is>
-      </c>
-      <c r="E216" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage252.png</t>
-        </is>
+      <c r="D216" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image251.png")</f>
+        <v/>
+      </c>
+      <c r="E216" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image252.png")</f>
+        <v/>
       </c>
       <c r="F216" s="42" t="n"/>
       <c r="G216" s="7" t="n"/>
@@ -6718,15 +6457,13 @@
           <t>1773371476904 - 1773371479305, 1773371483005 - 1773371484104, 1773371487604 - 1773371489004</t>
         </is>
       </c>
-      <c r="D217" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage253.png</t>
-        </is>
-      </c>
-      <c r="E217" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage254.png</t>
-        </is>
+      <c r="D217" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image253.png")</f>
+        <v/>
+      </c>
+      <c r="E217" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image254.png")</f>
+        <v/>
       </c>
       <c r="F217" s="56" t="n"/>
       <c r="G217" s="1" t="n"/>
@@ -6762,15 +6499,13 @@
           <t>1773371504505 - 1773371505304</t>
         </is>
       </c>
-      <c r="D219" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage255.png</t>
-        </is>
-      </c>
-      <c r="E219" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage256.png</t>
-        </is>
+      <c r="D219" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image255.png")</f>
+        <v/>
+      </c>
+      <c r="E219" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image256.png")</f>
+        <v/>
       </c>
       <c r="F219" s="56" t="n"/>
       <c r="G219" s="1" t="n"/>
@@ -6806,15 +6541,13 @@
           <t>1773371507204 - 1773371508205</t>
         </is>
       </c>
-      <c r="D221" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage257.png</t>
-        </is>
-      </c>
-      <c r="E221" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage258.png</t>
-        </is>
+      <c r="D221" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image257.png")</f>
+        <v/>
+      </c>
+      <c r="E221" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image258.png")</f>
+        <v/>
       </c>
       <c r="F221" s="56" t="n"/>
       <c r="G221" s="1" t="n"/>
@@ -6848,15 +6581,13 @@
       <c r="C223" s="16" t="n">
         <v>1773371509105</v>
       </c>
-      <c r="D223" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage259.png</t>
-        </is>
-      </c>
-      <c r="E223" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage260.png</t>
-        </is>
+      <c r="D223" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image259.png")</f>
+        <v/>
+      </c>
+      <c r="E223" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image260.png")</f>
+        <v/>
       </c>
       <c r="F223" s="42" t="n"/>
       <c r="G223" s="7" t="n"/>
@@ -6882,15 +6613,13 @@
           <t>1773371510004 - 1773371510805</t>
         </is>
       </c>
-      <c r="D224" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage261.png</t>
-        </is>
-      </c>
-      <c r="E224" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage262.png</t>
-        </is>
+      <c r="D224" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image261.png")</f>
+        <v/>
+      </c>
+      <c r="E224" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image262.png")</f>
+        <v/>
       </c>
       <c r="F224" s="42" t="n"/>
       <c r="G224" s="7" t="n"/>
@@ -6916,15 +6645,13 @@
           <t>1773371517805 - 1773371518705</t>
         </is>
       </c>
-      <c r="D225" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage263.png</t>
-        </is>
-      </c>
-      <c r="E225" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage264.png</t>
-        </is>
+      <c r="D225" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image263.png")</f>
+        <v/>
+      </c>
+      <c r="E225" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image264.png")</f>
+        <v/>
       </c>
       <c r="F225" s="42" t="n"/>
       <c r="G225" s="7" t="n"/>
@@ -6950,15 +6677,13 @@
           <t>1773371518805 - 1773371519904</t>
         </is>
       </c>
-      <c r="D226" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage265.png</t>
-        </is>
-      </c>
-      <c r="E226" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage263.png</t>
-        </is>
+      <c r="D226" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image265.png")</f>
+        <v/>
+      </c>
+      <c r="E226" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image263.png")</f>
+        <v/>
       </c>
       <c r="F226" s="42" t="n"/>
       <c r="G226" s="7" t="n"/>
@@ -6984,15 +6709,13 @@
           <t>1773371523105 - 1773371523804</t>
         </is>
       </c>
-      <c r="D227" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage266.png</t>
-        </is>
-      </c>
-      <c r="E227" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage267.png</t>
-        </is>
+      <c r="D227" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image266.png")</f>
+        <v/>
+      </c>
+      <c r="E227" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image267.png")</f>
+        <v/>
       </c>
       <c r="F227" s="56" t="n"/>
       <c r="G227" s="1" t="n"/>
@@ -7028,15 +6751,13 @@
           <t>1773371526105 - 1773371526305, 1773371526505, 1773371526605 - 1773371527504</t>
         </is>
       </c>
-      <c r="D229" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage268.png</t>
-        </is>
-      </c>
-      <c r="E229" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage269.png</t>
-        </is>
+      <c r="D229" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image268.png")</f>
+        <v/>
+      </c>
+      <c r="E229" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image269.png")</f>
+        <v/>
       </c>
       <c r="F229" s="56" t="n"/>
       <c r="G229" s="1" t="n"/>
@@ -7072,15 +6793,13 @@
           <t>1773371530105 - 1773371532004</t>
         </is>
       </c>
-      <c r="D231" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage270.png</t>
-        </is>
-      </c>
-      <c r="E231" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage271.png</t>
-        </is>
+      <c r="D231" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image270.png")</f>
+        <v/>
+      </c>
+      <c r="E231" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image271.png")</f>
+        <v/>
       </c>
       <c r="F231" s="42" t="n"/>
       <c r="G231" s="7" t="n"/>
@@ -7106,15 +6825,13 @@
           <t>1773371539304 - 1773371543905</t>
         </is>
       </c>
-      <c r="D232" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage272.png</t>
-        </is>
-      </c>
-      <c r="E232" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage273.png</t>
-        </is>
+      <c r="D232" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image272.png")</f>
+        <v/>
+      </c>
+      <c r="E232" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image273.png")</f>
+        <v/>
       </c>
       <c r="F232" s="56" t="n"/>
       <c r="G232" s="1" t="n"/>
@@ -7150,15 +6867,13 @@
           <t>1773371550004 - 1773371550905</t>
         </is>
       </c>
-      <c r="D234" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage274.png</t>
-        </is>
-      </c>
-      <c r="E234" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage275.png</t>
-        </is>
+      <c r="D234" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image274.png")</f>
+        <v/>
+      </c>
+      <c r="E234" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image275.png")</f>
+        <v/>
       </c>
       <c r="F234" s="42" t="n"/>
       <c r="G234" s="7" t="n"/>
@@ -7182,15 +6897,13 @@
       <c r="C235" s="16" t="n">
         <v>1773371556804</v>
       </c>
-      <c r="D235" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage276.png</t>
-        </is>
-      </c>
-      <c r="E235" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage277.png</t>
-        </is>
+      <c r="D235" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image276.png")</f>
+        <v/>
+      </c>
+      <c r="E235" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image277.png")</f>
+        <v/>
       </c>
       <c r="F235" s="42" t="n"/>
       <c r="G235" s="7" t="n"/>
@@ -7216,10 +6929,9 @@
           <t>1773371559800, 1773371560000</t>
         </is>
       </c>
-      <c r="D236" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage278.png</t>
-        </is>
+      <c r="D236" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image278.png")</f>
+        <v/>
       </c>
       <c r="E236" s="56" t="n"/>
       <c r="F236" s="56" t="n"/>
@@ -7256,15 +6968,13 @@
           <t>1773371561404 - 1773371562405</t>
         </is>
       </c>
-      <c r="D238" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage279.png</t>
-        </is>
-      </c>
-      <c r="E238" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage280.png</t>
-        </is>
+      <c r="D238" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image279.png")</f>
+        <v/>
+      </c>
+      <c r="E238" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image280.png")</f>
+        <v/>
       </c>
       <c r="F238" s="42" t="n"/>
       <c r="G238" s="7" t="n"/>
@@ -7288,10 +6998,9 @@
       <c r="C239" s="55" t="n">
         <v>1773371562200</v>
       </c>
-      <c r="D239" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage281.png</t>
-        </is>
+      <c r="D239" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image281.png")</f>
+        <v/>
       </c>
       <c r="E239" s="56" t="n"/>
       <c r="F239" s="56" t="n"/>
@@ -7328,15 +7037,13 @@
           <t>1773371561404 - 1773371562405</t>
         </is>
       </c>
-      <c r="D241" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage282.png</t>
-        </is>
-      </c>
-      <c r="E241" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage280.png</t>
-        </is>
+      <c r="D241" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image282.png")</f>
+        <v/>
+      </c>
+      <c r="E241" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image280.png")</f>
+        <v/>
       </c>
       <c r="F241" s="56" t="n"/>
       <c r="G241" s="1" t="n"/>
@@ -7372,10 +7079,9 @@
           <t xml:space="preserve">1773371563000, 1773371563300, 1773371564200, 1773371565000, 1773371565300 </t>
         </is>
       </c>
-      <c r="D243" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage283.png</t>
-        </is>
+      <c r="D243" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image283.png")</f>
+        <v/>
       </c>
       <c r="E243" s="42" t="n"/>
       <c r="F243" s="42" t="n"/>
@@ -7402,15 +7108,13 @@
           <t>1773371572604 - 1773371573905</t>
         </is>
       </c>
-      <c r="D244" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage284.png</t>
-        </is>
-      </c>
-      <c r="E244" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage285.png</t>
-        </is>
+      <c r="D244" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image284.png")</f>
+        <v/>
+      </c>
+      <c r="E244" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image285.png")</f>
+        <v/>
       </c>
       <c r="F244" s="42" t="n"/>
       <c r="G244" s="7" t="n"/>
@@ -7436,15 +7140,13 @@
           <t>1773371575105 - 1773371577305</t>
         </is>
       </c>
-      <c r="D245" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage286.png</t>
-        </is>
-      </c>
-      <c r="E245" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage287.png</t>
-        </is>
+      <c r="D245" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image286.png")</f>
+        <v/>
+      </c>
+      <c r="E245" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image287.png")</f>
+        <v/>
       </c>
       <c r="F245" s="42" t="n"/>
       <c r="G245" s="7" t="n"/>
@@ -7470,10 +7172,9 @@
           <t xml:space="preserve">1773371574800, 1773371578203, 1773371579403 </t>
         </is>
       </c>
-      <c r="D246" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage288.png</t>
-        </is>
+      <c r="D246" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image288.png")</f>
+        <v/>
       </c>
       <c r="E246" s="56" t="n"/>
       <c r="F246" s="56" t="n"/>
@@ -7510,15 +7211,13 @@
           <t>1773371583604 - 1773371584505</t>
         </is>
       </c>
-      <c r="D248" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage289.png</t>
-        </is>
-      </c>
-      <c r="E248" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage290.png</t>
-        </is>
+      <c r="D248" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image289.png")</f>
+        <v/>
+      </c>
+      <c r="E248" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image290.png")</f>
+        <v/>
       </c>
       <c r="F248" s="42" t="n"/>
       <c r="G248" s="7" t="n"/>
@@ -7542,10 +7241,9 @@
       <c r="C249" s="55" t="n">
         <v>1773371584600</v>
       </c>
-      <c r="D249" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage291.png</t>
-        </is>
+      <c r="D249" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image291.png")</f>
+        <v/>
       </c>
       <c r="E249" s="56" t="n"/>
       <c r="F249" s="56" t="n"/>
@@ -7582,15 +7280,13 @@
           <t>1773371585005, 1773371585505, 1773371585904</t>
         </is>
       </c>
-      <c r="D251" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage292.png</t>
-        </is>
-      </c>
-      <c r="E251" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage293.png</t>
-        </is>
+      <c r="D251" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image292.png")</f>
+        <v/>
+      </c>
+      <c r="E251" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image293.png")</f>
+        <v/>
       </c>
       <c r="F251" s="42" t="n"/>
       <c r="G251" s="7" t="n"/>
@@ -7614,10 +7310,9 @@
       <c r="C252" s="55" t="n">
         <v>1773371587603</v>
       </c>
-      <c r="D252" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage294.png</t>
-        </is>
+      <c r="D252" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image294.png")</f>
+        <v/>
       </c>
       <c r="E252" s="56" t="n"/>
       <c r="F252" s="56" t="n"/>
@@ -7654,15 +7349,13 @@
           <t>1773371587705, 1773371588104, 1773371588203, 1773371588804 - 1773371589205, 1773371589403, 1773371589704, 1773371589803, 1773371590003, 1773371590203, 1773371590403, 1773371590905 - 1773371591304</t>
         </is>
       </c>
-      <c r="D254" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage295.png</t>
-        </is>
-      </c>
-      <c r="E254" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage296.png</t>
-        </is>
+      <c r="D254" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image295.png")</f>
+        <v/>
+      </c>
+      <c r="E254" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image296.png")</f>
+        <v/>
       </c>
       <c r="F254" s="56" t="n"/>
       <c r="G254" s="1" t="n"/>
@@ -7696,15 +7389,13 @@
       <c r="C256" s="55" t="n">
         <v>1773371594504</v>
       </c>
-      <c r="D256" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage297.png</t>
-        </is>
-      </c>
-      <c r="E256" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage298.png</t>
-        </is>
+      <c r="D256" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image297.png")</f>
+        <v/>
+      </c>
+      <c r="E256" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image298.png")</f>
+        <v/>
       </c>
       <c r="F256" s="56" t="n"/>
       <c r="G256" s="1" t="n"/>
@@ -7740,15 +7431,13 @@
           <t>1773371598905 - 1773371603904</t>
         </is>
       </c>
-      <c r="D258" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage299.png</t>
-        </is>
-      </c>
-      <c r="E258" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage300.png</t>
-        </is>
+      <c r="D258" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image299.png")</f>
+        <v/>
+      </c>
+      <c r="E258" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image300.png")</f>
+        <v/>
       </c>
       <c r="F258" s="56" t="n"/>
       <c r="G258" s="1" t="n"/>
@@ -7784,15 +7473,13 @@
           <t>1773371604005 - 1773371604604</t>
         </is>
       </c>
-      <c r="D260" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage301.png</t>
-        </is>
-      </c>
-      <c r="E260" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage302.png</t>
-        </is>
+      <c r="D260" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image301.png")</f>
+        <v/>
+      </c>
+      <c r="E260" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image302.png")</f>
+        <v/>
       </c>
       <c r="F260" s="42" t="n"/>
       <c r="G260" s="7" t="n"/>
@@ -7818,15 +7505,13 @@
           <t>1773371606605 - 1773371607604</t>
         </is>
       </c>
-      <c r="D261" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage303.png</t>
-        </is>
-      </c>
-      <c r="E261" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage304.png</t>
-        </is>
+      <c r="D261" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image303.png")</f>
+        <v/>
+      </c>
+      <c r="E261" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image304.png")</f>
+        <v/>
       </c>
       <c r="F261" s="56" t="n"/>
       <c r="G261" s="1" t="n"/>
@@ -7862,15 +7547,13 @@
           <t>1773371614704 - 1773371615504</t>
         </is>
       </c>
-      <c r="D263" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage305.png</t>
-        </is>
-      </c>
-      <c r="E263" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage306.png</t>
-        </is>
+      <c r="D263" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image305.png")</f>
+        <v/>
+      </c>
+      <c r="E263" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image306.png")</f>
+        <v/>
       </c>
       <c r="F263" s="56" t="n"/>
       <c r="G263" s="1" t="n"/>
@@ -7906,10 +7589,9 @@
           <t>1773371616603, 1773371617103</t>
         </is>
       </c>
-      <c r="D265" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage307.png</t>
-        </is>
+      <c r="D265" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image307.png")</f>
+        <v/>
       </c>
       <c r="E265" s="42" t="n"/>
       <c r="F265" s="42" t="n"/>
@@ -7934,15 +7616,13 @@
       <c r="C266" s="55" t="n">
         <v>1773371617905</v>
       </c>
-      <c r="D266" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage308.png</t>
-        </is>
-      </c>
-      <c r="E266" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage309.png</t>
-        </is>
+      <c r="D266" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image308.png")</f>
+        <v/>
+      </c>
+      <c r="E266" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image309.png")</f>
+        <v/>
       </c>
       <c r="F266" s="56" t="n"/>
       <c r="G266" s="1" t="n"/>
@@ -7978,10 +7658,9 @@
           <t xml:space="preserve">1773371618603, 1773371619303, 1773371622100, 1773371625803, 1773371626203, 1773371626503 </t>
         </is>
       </c>
-      <c r="D268" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage310.png</t>
-        </is>
+      <c r="D268" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image310.png")</f>
+        <v/>
       </c>
       <c r="E268" s="42" t="n"/>
       <c r="F268" s="42" t="n"/>
@@ -8006,15 +7685,13 @@
       <c r="C269" s="16" t="n">
         <v>1773371643303</v>
       </c>
-      <c r="D269" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage311.png</t>
-        </is>
-      </c>
-      <c r="E269" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage312.png</t>
-        </is>
+      <c r="D269" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image311.png")</f>
+        <v/>
+      </c>
+      <c r="E269" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image312.png")</f>
+        <v/>
       </c>
       <c r="F269" s="42" t="n"/>
       <c r="G269" s="7" t="n"/>
@@ -8040,15 +7717,13 @@
           <t>1773371651105 - 1773371651904</t>
         </is>
       </c>
-      <c r="D270" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage313.png</t>
-        </is>
-      </c>
-      <c r="E270" s="25" t="inlineStr">
-        <is>
-          <t>replaced with urlimage314.png</t>
-        </is>
+      <c r="D270" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image313.png")</f>
+        <v/>
+      </c>
+      <c r="E270" s="25">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image314.png")</f>
+        <v/>
       </c>
       <c r="F270" s="42" t="n"/>
       <c r="G270" s="7" t="n"/>
@@ -8072,10 +7747,9 @@
       <c r="C271" s="55" t="n">
         <v>1773371653803</v>
       </c>
-      <c r="D271" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage315.png</t>
-        </is>
+      <c r="D271" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image315.png")</f>
+        <v/>
       </c>
       <c r="E271" s="56" t="n"/>
       <c r="F271" s="56" t="n"/>
@@ -8722,15 +8396,13 @@
       <c r="C2" s="18" t="n">
         <v>1773372387004</v>
       </c>
-      <c r="D2" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage316.png</t>
-        </is>
-      </c>
-      <c r="E2" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage317.png</t>
-        </is>
+      <c r="D2" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image316.png")</f>
+        <v/>
+      </c>
+      <c r="E2" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image317.png")</f>
+        <v/>
       </c>
       <c r="F2" s="56" t="n"/>
       <c r="G2" s="1" t="inlineStr">
@@ -8773,20 +8445,17 @@
       <c r="C5" s="18" t="n">
         <v>1773372395804</v>
       </c>
-      <c r="D5" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage318.png</t>
-        </is>
-      </c>
-      <c r="E5" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage319.png</t>
-        </is>
-      </c>
-      <c r="F5" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage320.png</t>
-        </is>
+      <c r="D5" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image318.png")</f>
+        <v/>
+      </c>
+      <c r="E5" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image319.png")</f>
+        <v/>
+      </c>
+      <c r="F5" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image320.png")</f>
+        <v/>
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
@@ -8830,15 +8499,13 @@
       <c r="C8" s="18" t="n">
         <v>1773372408604</v>
       </c>
-      <c r="D8" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage321.png</t>
-        </is>
-      </c>
-      <c r="E8" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage322.png</t>
-        </is>
+      <c r="D8" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image321.png")</f>
+        <v/>
+      </c>
+      <c r="E8" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image322.png")</f>
+        <v/>
       </c>
       <c r="F8" s="56" t="n"/>
       <c r="G8" s="1" t="inlineStr">
@@ -8872,15 +8539,13 @@
       <c r="C10" s="18" t="n">
         <v>1773372412800</v>
       </c>
-      <c r="D10" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage323.png</t>
-        </is>
-      </c>
-      <c r="E10" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage324.png</t>
-        </is>
+      <c r="D10" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image323.png")</f>
+        <v/>
+      </c>
+      <c r="E10" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image324.png")</f>
+        <v/>
       </c>
       <c r="F10" s="56" t="n"/>
       <c r="G10" s="1" t="inlineStr">
@@ -8923,20 +8588,17 @@
       <c r="C13" s="18" t="n">
         <v>1773372426204</v>
       </c>
-      <c r="D13" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage325.png</t>
-        </is>
-      </c>
-      <c r="E13" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage326.png</t>
-        </is>
-      </c>
-      <c r="F13" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage327.png</t>
-        </is>
+      <c r="D13" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image325.png")</f>
+        <v/>
+      </c>
+      <c r="E13" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image326.png")</f>
+        <v/>
+      </c>
+      <c r="F13" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image327.png")</f>
+        <v/>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -9039,15 +8701,13 @@
       <c r="C21" s="18" t="n">
         <v>1773372648205</v>
       </c>
-      <c r="D21" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage328.png</t>
-        </is>
-      </c>
-      <c r="E21" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage329.png</t>
-        </is>
+      <c r="D21" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image328.png")</f>
+        <v/>
+      </c>
+      <c r="E21" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image329.png")</f>
+        <v/>
       </c>
       <c r="F21" s="56" t="n"/>
       <c r="G21" s="1" t="inlineStr">
@@ -9081,20 +8741,17 @@
       <c r="C23" s="18" t="n">
         <v>1773372750905</v>
       </c>
-      <c r="D23" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage330.png</t>
-        </is>
-      </c>
-      <c r="E23" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage331.png</t>
-        </is>
-      </c>
-      <c r="F23" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage332.png</t>
-        </is>
+      <c r="D23" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image330.png")</f>
+        <v/>
+      </c>
+      <c r="E23" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image331.png")</f>
+        <v/>
+      </c>
+      <c r="F23" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image332.png")</f>
+        <v/>
       </c>
       <c r="G23" s="1" t="inlineStr">
         <is>
@@ -9182,15 +8839,13 @@
       <c r="C30" s="18" t="n">
         <v>1773372831805</v>
       </c>
-      <c r="D30" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage333.png</t>
-        </is>
-      </c>
-      <c r="E30" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage334.png</t>
-        </is>
+      <c r="D30" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image333.png")</f>
+        <v/>
+      </c>
+      <c r="E30" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image334.png")</f>
+        <v/>
       </c>
       <c r="F30" s="56" t="n"/>
       <c r="G30" s="1" t="inlineStr">
@@ -9233,20 +8888,17 @@
       <c r="C33" s="18" t="n">
         <v>1773372847304</v>
       </c>
-      <c r="D33" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage335.png</t>
-        </is>
-      </c>
-      <c r="E33" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage336.png</t>
-        </is>
-      </c>
-      <c r="F33" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage337.png</t>
-        </is>
+      <c r="D33" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image335.png")</f>
+        <v/>
+      </c>
+      <c r="E33" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image336.png")</f>
+        <v/>
+      </c>
+      <c r="F33" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image337.png")</f>
+        <v/>
       </c>
       <c r="G33" s="1" t="inlineStr">
         <is>
@@ -9389,15 +9041,13 @@
       <c r="C45" s="18" t="n">
         <v>1773372878604</v>
       </c>
-      <c r="D45" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage338.png</t>
-        </is>
-      </c>
-      <c r="E45" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage339.png</t>
-        </is>
+      <c r="D45" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image338.png")</f>
+        <v/>
+      </c>
+      <c r="E45" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image339.png")</f>
+        <v/>
       </c>
       <c r="F45" s="56" t="n"/>
       <c r="G45" s="1" t="inlineStr">
@@ -9431,20 +9081,17 @@
       <c r="C47" s="18" t="n">
         <v>1773372879604</v>
       </c>
-      <c r="D47" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage339.png</t>
-        </is>
-      </c>
-      <c r="E47" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage340.png</t>
-        </is>
-      </c>
-      <c r="F47" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage341.png</t>
-        </is>
+      <c r="D47" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image339.png")</f>
+        <v/>
+      </c>
+      <c r="E47" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image340.png")</f>
+        <v/>
+      </c>
+      <c r="F47" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image341.png")</f>
+        <v/>
       </c>
       <c r="G47" s="1" t="inlineStr">
         <is>
@@ -9499,15 +9146,13 @@
       <c r="C51" s="18" t="n">
         <v>1773372925305</v>
       </c>
-      <c r="D51" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage342.png</t>
-        </is>
-      </c>
-      <c r="E51" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage343.png</t>
-        </is>
+      <c r="D51" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image342.png")</f>
+        <v/>
+      </c>
+      <c r="E51" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image343.png")</f>
+        <v/>
       </c>
       <c r="F51" s="56" t="n"/>
       <c r="G51" s="1" t="inlineStr">
@@ -9541,20 +9186,17 @@
       <c r="C53" s="18" t="n">
         <v>1773372982904</v>
       </c>
-      <c r="D53" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage344.png</t>
-        </is>
-      </c>
-      <c r="E53" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage345.png</t>
-        </is>
-      </c>
-      <c r="F53" s="64" t="inlineStr">
-        <is>
-          <t>replaced with urlimage346.png</t>
-        </is>
+      <c r="D53" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image344.png")</f>
+        <v/>
+      </c>
+      <c r="E53" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image345.png")</f>
+        <v/>
+      </c>
+      <c r="F53" s="64">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image346.png")</f>
+        <v/>
       </c>
       <c r="G53" s="1" t="inlineStr">
         <is>
@@ -9738,15 +9380,13 @@
           <t>1773293878403 - 1773293886103</t>
         </is>
       </c>
-      <c r="D2" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage347.png</t>
-        </is>
-      </c>
-      <c r="E2" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage348.png</t>
-        </is>
+      <c r="D2" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image347.png")</f>
+        <v/>
+      </c>
+      <c r="E2" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image348.png")</f>
+        <v/>
       </c>
       <c r="F2" s="56" t="n"/>
       <c r="G2" s="1" t="inlineStr">
@@ -9780,15 +9420,13 @@
           <t>1773293886603 - 1773293895803</t>
         </is>
       </c>
-      <c r="D4" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage349.png</t>
-        </is>
-      </c>
-      <c r="E4" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage348.png</t>
-        </is>
+      <c r="D4" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image349.png")</f>
+        <v/>
+      </c>
+      <c r="E4" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image348.png")</f>
+        <v/>
       </c>
       <c r="F4" s="42" t="n"/>
       <c r="G4" s="7" t="inlineStr">
@@ -9813,15 +9451,13 @@
           <t>1773293896003 - 1773293898303</t>
         </is>
       </c>
-      <c r="D5" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage348.png</t>
-        </is>
-      </c>
-      <c r="E5" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage350.png</t>
-        </is>
+      <c r="D5" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image348.png")</f>
+        <v/>
+      </c>
+      <c r="E5" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image350.png")</f>
+        <v/>
       </c>
       <c r="F5" s="42" t="n"/>
       <c r="G5" s="7" t="inlineStr">
@@ -9846,15 +9482,13 @@
           <t>1773293906403 - 1773293914403</t>
         </is>
       </c>
-      <c r="D6" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage351.png</t>
-        </is>
-      </c>
-      <c r="E6" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage352.png</t>
-        </is>
+      <c r="D6" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image351.png")</f>
+        <v/>
+      </c>
+      <c r="E6" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image352.png")</f>
+        <v/>
       </c>
       <c r="F6" s="42" t="n"/>
       <c r="G6" s="7" t="inlineStr">
@@ -9879,15 +9513,13 @@
           <t>1773293919304 - 1773293928504</t>
         </is>
       </c>
-      <c r="D7" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage353.png</t>
-        </is>
-      </c>
-      <c r="E7" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage354.png</t>
-        </is>
+      <c r="D7" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image353.png")</f>
+        <v/>
+      </c>
+      <c r="E7" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image354.png")</f>
+        <v/>
       </c>
       <c r="F7" s="42" t="n"/>
       <c r="G7" s="7" t="inlineStr">
@@ -9912,15 +9544,13 @@
           <t>1773293929604 - 1773293930604</t>
         </is>
       </c>
-      <c r="D8" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage355.png</t>
-        </is>
-      </c>
-      <c r="E8" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage356.png</t>
-        </is>
+      <c r="D8" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image355.png")</f>
+        <v/>
+      </c>
+      <c r="E8" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image356.png")</f>
+        <v/>
       </c>
       <c r="F8" s="56" t="n"/>
       <c r="G8" s="1" t="inlineStr">
@@ -9954,15 +9584,13 @@
           <t>1773293930704 - 1773293931404, 1773293932504 - 1773293934104</t>
         </is>
       </c>
-      <c r="D10" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage357.png</t>
-        </is>
-      </c>
-      <c r="E10" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage358.png</t>
-        </is>
+      <c r="D10" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image357.png")</f>
+        <v/>
+      </c>
+      <c r="E10" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image358.png")</f>
+        <v/>
       </c>
       <c r="F10" s="42" t="n"/>
       <c r="G10" s="7" t="inlineStr">
@@ -9987,15 +9615,13 @@
           <t>1773293934104 - 1773293936305</t>
         </is>
       </c>
-      <c r="D11" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage359.png</t>
-        </is>
-      </c>
-      <c r="E11" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage360.png</t>
-        </is>
+      <c r="D11" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image359.png")</f>
+        <v/>
+      </c>
+      <c r="E11" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image360.png")</f>
+        <v/>
       </c>
       <c r="F11" s="56" t="n"/>
       <c r="G11" s="1" t="inlineStr">
@@ -10029,15 +9655,13 @@
           <t>1773293938405 - 1773293940603</t>
         </is>
       </c>
-      <c r="D13" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage361.png</t>
-        </is>
-      </c>
-      <c r="E13" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage362.png</t>
-        </is>
+      <c r="D13" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image361.png")</f>
+        <v/>
+      </c>
+      <c r="E13" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image362.png")</f>
+        <v/>
       </c>
       <c r="F13" s="56" t="n"/>
       <c r="G13" s="1" t="inlineStr">
@@ -10071,15 +9695,13 @@
           <t>1773293941504 - 1773293945004</t>
         </is>
       </c>
-      <c r="D15" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage363.png</t>
-        </is>
-      </c>
-      <c r="E15" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage364.png</t>
-        </is>
+      <c r="D15" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image363.png")</f>
+        <v/>
+      </c>
+      <c r="E15" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image364.png")</f>
+        <v/>
       </c>
       <c r="F15" s="56" t="n"/>
       <c r="G15" s="1" t="inlineStr">
@@ -10113,15 +9735,13 @@
           <t>1773293945104  - 1773293947705</t>
         </is>
       </c>
-      <c r="D17" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage365.png</t>
-        </is>
-      </c>
-      <c r="E17" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage366.png</t>
-        </is>
+      <c r="D17" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image365.png")</f>
+        <v/>
+      </c>
+      <c r="E17" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image366.png")</f>
+        <v/>
       </c>
       <c r="F17" s="56" t="n"/>
       <c r="G17" s="1" t="inlineStr">
@@ -10155,15 +9775,13 @@
           <t>1773293948805 - 1773293949704</t>
         </is>
       </c>
-      <c r="D19" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage367.png</t>
-        </is>
-      </c>
-      <c r="E19" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage368.png</t>
-        </is>
+      <c r="D19" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image367.png")</f>
+        <v/>
+      </c>
+      <c r="E19" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image368.png")</f>
+        <v/>
       </c>
       <c r="F19" s="56" t="n"/>
       <c r="G19" s="1" t="inlineStr">
@@ -10197,15 +9815,13 @@
           <t>1773293951105 - 1773293952105</t>
         </is>
       </c>
-      <c r="D21" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage369.png</t>
-        </is>
-      </c>
-      <c r="E21" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage370.png</t>
-        </is>
+      <c r="D21" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image369.png")</f>
+        <v/>
+      </c>
+      <c r="E21" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image370.png")</f>
+        <v/>
       </c>
       <c r="F21" s="42" t="n"/>
       <c r="G21" s="7" t="inlineStr">
@@ -10230,15 +9846,13 @@
           <t>1773293952204 - 1773293953304, 1773293954504 - 1773293955704</t>
         </is>
       </c>
-      <c r="D22" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage371.png</t>
-        </is>
-      </c>
-      <c r="E22" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage372.png</t>
-        </is>
+      <c r="D22" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image371.png")</f>
+        <v/>
+      </c>
+      <c r="E22" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image372.png")</f>
+        <v/>
       </c>
       <c r="F22" s="56" t="n"/>
       <c r="G22" s="1" t="inlineStr">
@@ -10272,15 +9886,13 @@
           <t>1773293957004 - 1773293958304</t>
         </is>
       </c>
-      <c r="D24" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage373.png</t>
-        </is>
-      </c>
-      <c r="E24" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage374.png</t>
-        </is>
+      <c r="D24" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image373.png")</f>
+        <v/>
+      </c>
+      <c r="E24" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image374.png")</f>
+        <v/>
       </c>
       <c r="F24" s="56" t="n"/>
       <c r="G24" s="1" t="inlineStr">
@@ -10314,15 +9926,13 @@
           <t>1773293959505 - 1773293960405</t>
         </is>
       </c>
-      <c r="D26" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage375.png</t>
-        </is>
-      </c>
-      <c r="E26" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage376.png</t>
-        </is>
+      <c r="D26" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image375.png")</f>
+        <v/>
+      </c>
+      <c r="E26" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image376.png")</f>
+        <v/>
       </c>
       <c r="F26" s="56" t="n"/>
       <c r="G26" s="1" t="inlineStr">
@@ -10356,15 +9966,13 @@
           <t>1773293962604 - 1773293963804</t>
         </is>
       </c>
-      <c r="D28" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage377.png</t>
-        </is>
-      </c>
-      <c r="E28" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage378.png</t>
-        </is>
+      <c r="D28" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image377.png")</f>
+        <v/>
+      </c>
+      <c r="E28" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image378.png")</f>
+        <v/>
       </c>
       <c r="F28" s="56" t="n"/>
       <c r="G28" s="1" t="inlineStr">
@@ -10398,15 +10006,13 @@
           <t>1773293969104 - 1773293970104</t>
         </is>
       </c>
-      <c r="D30" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage379.png</t>
-        </is>
-      </c>
-      <c r="E30" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage380.png</t>
-        </is>
+      <c r="D30" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image379.png")</f>
+        <v/>
+      </c>
+      <c r="E30" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image380.png")</f>
+        <v/>
       </c>
       <c r="F30" s="56" t="n"/>
       <c r="G30" s="1" t="inlineStr">
@@ -10440,15 +10046,13 @@
           <t>1773293970205 - 1773293972205</t>
         </is>
       </c>
-      <c r="D32" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage381.png</t>
-        </is>
-      </c>
-      <c r="E32" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage382.png</t>
-        </is>
+      <c r="D32" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image381.png")</f>
+        <v/>
+      </c>
+      <c r="E32" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image382.png")</f>
+        <v/>
       </c>
       <c r="F32" s="56" t="n"/>
       <c r="G32" s="1" t="inlineStr">
@@ -10482,15 +10086,13 @@
           <t>1773293972305 - 1773293979504</t>
         </is>
       </c>
-      <c r="D34" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage383.png</t>
-        </is>
-      </c>
-      <c r="E34" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage384.png</t>
-        </is>
+      <c r="D34" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image383.png")</f>
+        <v/>
+      </c>
+      <c r="E34" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image384.png")</f>
+        <v/>
       </c>
       <c r="F34" s="56" t="n"/>
       <c r="G34" s="1" t="inlineStr">
@@ -10524,15 +10126,13 @@
           <t>1773293980705 - 1773293983405</t>
         </is>
       </c>
-      <c r="D36" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage385.png</t>
-        </is>
-      </c>
-      <c r="E36" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage386.png</t>
-        </is>
+      <c r="D36" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image385.png")</f>
+        <v/>
+      </c>
+      <c r="E36" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image386.png")</f>
+        <v/>
       </c>
       <c r="F36" s="42" t="n"/>
       <c r="G36" s="7" t="inlineStr">
@@ -10557,15 +10157,13 @@
           <t>1773293989304 - 1773293990104</t>
         </is>
       </c>
-      <c r="D37" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage387.png</t>
-        </is>
-      </c>
-      <c r="E37" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage388.png</t>
-        </is>
+      <c r="D37" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image387.png")</f>
+        <v/>
+      </c>
+      <c r="E37" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image388.png")</f>
+        <v/>
       </c>
       <c r="F37" s="56" t="n"/>
       <c r="G37" s="1" t="inlineStr">
@@ -10599,15 +10197,13 @@
           <t>1773293993305 - 1773293994205</t>
         </is>
       </c>
-      <c r="D39" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage389.png</t>
-        </is>
-      </c>
-      <c r="E39" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage390.png</t>
-        </is>
+      <c r="D39" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image389.png")</f>
+        <v/>
+      </c>
+      <c r="E39" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image390.png")</f>
+        <v/>
       </c>
       <c r="F39" s="42" t="n"/>
       <c r="G39" s="7" t="inlineStr">
@@ -10632,15 +10228,13 @@
           <t>1773294004605 - 1773294005505</t>
         </is>
       </c>
-      <c r="D40" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage391.png</t>
-        </is>
-      </c>
-      <c r="E40" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage392.png</t>
-        </is>
+      <c r="D40" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image391.png")</f>
+        <v/>
+      </c>
+      <c r="E40" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image392.png")</f>
+        <v/>
       </c>
       <c r="F40" s="42" t="n"/>
       <c r="G40" s="7" t="inlineStr">
@@ -10665,15 +10259,13 @@
           <t>1773294008604 - 1773294010504</t>
         </is>
       </c>
-      <c r="D41" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage393.png</t>
-        </is>
-      </c>
-      <c r="E41" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage394.png</t>
-        </is>
+      <c r="D41" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image393.png")</f>
+        <v/>
+      </c>
+      <c r="E41" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image394.png")</f>
+        <v/>
       </c>
       <c r="F41" s="42" t="n"/>
       <c r="G41" s="7" t="inlineStr">
@@ -10698,15 +10290,13 @@
           <t>1773294016605 - 1773294017505</t>
         </is>
       </c>
-      <c r="D42" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage395.png</t>
-        </is>
-      </c>
-      <c r="E42" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage396.png</t>
-        </is>
+      <c r="D42" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image395.png")</f>
+        <v/>
+      </c>
+      <c r="E42" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image396.png")</f>
+        <v/>
       </c>
       <c r="F42" s="42" t="n"/>
       <c r="G42" s="7" t="inlineStr">
@@ -10731,15 +10321,13 @@
           <t>1773294018604 - 1773294019504</t>
         </is>
       </c>
-      <c r="D43" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage397.png</t>
-        </is>
-      </c>
-      <c r="E43" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage398.png</t>
-        </is>
+      <c r="D43" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image397.png")</f>
+        <v/>
+      </c>
+      <c r="E43" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image398.png")</f>
+        <v/>
       </c>
       <c r="F43" s="56" t="n"/>
       <c r="G43" s="1" t="inlineStr">
@@ -10773,15 +10361,13 @@
           <t>1773294019604 - 1773294020704</t>
         </is>
       </c>
-      <c r="D45" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage399.png</t>
-        </is>
-      </c>
-      <c r="E45" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage400.png</t>
-        </is>
+      <c r="D45" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image399.png")</f>
+        <v/>
+      </c>
+      <c r="E45" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image400.png")</f>
+        <v/>
       </c>
       <c r="F45" s="56" t="n"/>
       <c r="G45" s="1" t="inlineStr">
@@ -10815,15 +10401,13 @@
           <t>1773294022704 - 1773294023504</t>
         </is>
       </c>
-      <c r="D47" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage401.png</t>
-        </is>
-      </c>
-      <c r="E47" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage402.png</t>
-        </is>
+      <c r="D47" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image401.png")</f>
+        <v/>
+      </c>
+      <c r="E47" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image402.png")</f>
+        <v/>
       </c>
       <c r="F47" s="56" t="n"/>
       <c r="G47" s="1" t="inlineStr">
@@ -10857,15 +10441,13 @@
           <t>1773294024804 - 1773294025905</t>
         </is>
       </c>
-      <c r="D49" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage403.png</t>
-        </is>
-      </c>
-      <c r="E49" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage404.png</t>
-        </is>
+      <c r="D49" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image403.png")</f>
+        <v/>
+      </c>
+      <c r="E49" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image404.png")</f>
+        <v/>
       </c>
       <c r="F49" s="56" t="n"/>
       <c r="G49" s="1" t="inlineStr">
@@ -10899,15 +10481,13 @@
           <t>1773294040904 - 1773294041804</t>
         </is>
       </c>
-      <c r="D51" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage405.png</t>
-        </is>
-      </c>
-      <c r="E51" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage406.png</t>
-        </is>
+      <c r="D51" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image405.png")</f>
+        <v/>
+      </c>
+      <c r="E51" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image406.png")</f>
+        <v/>
       </c>
       <c r="F51" s="42" t="n"/>
       <c r="G51" s="7" t="inlineStr">
@@ -10932,15 +10512,13 @@
           <t>1773294044905 - 1773294045805</t>
         </is>
       </c>
-      <c r="D52" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage407.png</t>
-        </is>
-      </c>
-      <c r="E52" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage408.png</t>
-        </is>
+      <c r="D52" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image407.png")</f>
+        <v/>
+      </c>
+      <c r="E52" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image408.png")</f>
+        <v/>
       </c>
       <c r="F52" s="42" t="n"/>
       <c r="G52" s="7" t="inlineStr">
@@ -10965,15 +10543,13 @@
           <t>1773294045905 - 1773294046905</t>
         </is>
       </c>
-      <c r="D53" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage409.png</t>
-        </is>
-      </c>
-      <c r="E53" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage410.png</t>
-        </is>
+      <c r="D53" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image409.png")</f>
+        <v/>
+      </c>
+      <c r="E53" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image410.png")</f>
+        <v/>
       </c>
       <c r="F53" s="42" t="n"/>
       <c r="G53" s="7" t="inlineStr">
@@ -10998,15 +10574,13 @@
           <t>1773294048005 - 1773294048904</t>
         </is>
       </c>
-      <c r="D54" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage411.png</t>
-        </is>
-      </c>
-      <c r="E54" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage412.png</t>
-        </is>
+      <c r="D54" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image411.png")</f>
+        <v/>
+      </c>
+      <c r="E54" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image412.png")</f>
+        <v/>
       </c>
       <c r="F54" s="42" t="n"/>
       <c r="G54" s="7" t="inlineStr">
@@ -11031,15 +10605,13 @@
           <t>1773294050005 - 1773294051904</t>
         </is>
       </c>
-      <c r="D55" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage413.png</t>
-        </is>
-      </c>
-      <c r="E55" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage414.png</t>
-        </is>
+      <c r="D55" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image413.png")</f>
+        <v/>
+      </c>
+      <c r="E55" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image414.png")</f>
+        <v/>
       </c>
       <c r="F55" s="42" t="n"/>
       <c r="G55" s="7" t="inlineStr">
@@ -11064,15 +10636,13 @@
           <t>1773294052804 - 1773294055405</t>
         </is>
       </c>
-      <c r="D56" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage415.png</t>
-        </is>
-      </c>
-      <c r="E56" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage416.png</t>
-        </is>
+      <c r="D56" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image415.png")</f>
+        <v/>
+      </c>
+      <c r="E56" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image416.png")</f>
+        <v/>
       </c>
       <c r="F56" s="42" t="n"/>
       <c r="G56" s="7" t="inlineStr">
@@ -11097,15 +10667,13 @@
           <t>1773294056505, 1773294056605</t>
         </is>
       </c>
-      <c r="D57" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage417.png</t>
-        </is>
-      </c>
-      <c r="E57" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage418.png</t>
-        </is>
+      <c r="D57" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image417.png")</f>
+        <v/>
+      </c>
+      <c r="E57" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image418.png")</f>
+        <v/>
       </c>
       <c r="F57" s="42" t="n"/>
       <c r="G57" s="7" t="inlineStr">
@@ -11130,15 +10698,13 @@
           <t>1773294058704 - 1773294059704</t>
         </is>
       </c>
-      <c r="D58" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage419.png</t>
-        </is>
-      </c>
-      <c r="E58" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage419.png</t>
-        </is>
+      <c r="D58" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image419.png")</f>
+        <v/>
+      </c>
+      <c r="E58" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image419.png")</f>
+        <v/>
       </c>
       <c r="F58" s="42" t="n"/>
       <c r="G58" s="7" t="inlineStr">
@@ -11163,15 +10729,13 @@
           <t>1773294060804 - 1773294061704</t>
         </is>
       </c>
-      <c r="D59" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage420.png</t>
-        </is>
-      </c>
-      <c r="E59" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage421.png</t>
-        </is>
+      <c r="D59" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image420.png")</f>
+        <v/>
+      </c>
+      <c r="E59" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image421.png")</f>
+        <v/>
       </c>
       <c r="F59" s="42" t="n"/>
       <c r="G59" s="7" t="inlineStr">
@@ -11196,15 +10760,13 @@
           <t>1773294063805 - 1773294065705</t>
         </is>
       </c>
-      <c r="D60" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage422.png</t>
-        </is>
-      </c>
-      <c r="E60" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage423.png</t>
-        </is>
+      <c r="D60" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image422.png")</f>
+        <v/>
+      </c>
+      <c r="E60" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image423.png")</f>
+        <v/>
       </c>
       <c r="F60" s="42" t="n"/>
       <c r="G60" s="7" t="inlineStr">
@@ -11229,15 +10791,13 @@
           <t>1773294065804 - 1773294066704</t>
         </is>
       </c>
-      <c r="D61" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage424.png</t>
-        </is>
-      </c>
-      <c r="E61" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage425.png</t>
-        </is>
+      <c r="D61" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image424.png")</f>
+        <v/>
+      </c>
+      <c r="E61" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image425.png")</f>
+        <v/>
       </c>
       <c r="F61" s="56" t="n"/>
       <c r="G61" s="1" t="inlineStr">
@@ -11271,15 +10831,13 @@
           <t>1773294077404 - 1773294078604</t>
         </is>
       </c>
-      <c r="D63" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage426.png</t>
-        </is>
-      </c>
-      <c r="E63" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage427.png</t>
-        </is>
+      <c r="D63" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image426.png")</f>
+        <v/>
+      </c>
+      <c r="E63" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image427.png")</f>
+        <v/>
       </c>
       <c r="F63" s="56" t="n"/>
       <c r="G63" s="1" t="inlineStr">
@@ -11313,15 +10871,13 @@
           <t>1773294080705 - 1773294081605</t>
         </is>
       </c>
-      <c r="D65" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage428.png</t>
-        </is>
-      </c>
-      <c r="E65" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage429.png</t>
-        </is>
+      <c r="D65" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image428.png")</f>
+        <v/>
+      </c>
+      <c r="E65" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image429.png")</f>
+        <v/>
       </c>
       <c r="F65" s="56" t="n"/>
       <c r="G65" s="1" t="inlineStr">
@@ -11355,15 +10911,13 @@
           <t>1773294089004 - 1773294090404</t>
         </is>
       </c>
-      <c r="D67" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage430.png</t>
-        </is>
-      </c>
-      <c r="E67" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage431.png</t>
-        </is>
+      <c r="D67" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image430.png")</f>
+        <v/>
+      </c>
+      <c r="E67" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image431.png")</f>
+        <v/>
       </c>
       <c r="F67" s="56" t="n"/>
       <c r="G67" s="1" t="inlineStr">
@@ -11397,15 +10951,13 @@
           <t>1773294092505 - 1773294093405</t>
         </is>
       </c>
-      <c r="D69" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage432.png</t>
-        </is>
-      </c>
-      <c r="E69" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage433.png</t>
-        </is>
+      <c r="D69" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image432.png")</f>
+        <v/>
+      </c>
+      <c r="E69" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image433.png")</f>
+        <v/>
       </c>
       <c r="F69" s="56" t="n"/>
       <c r="G69" s="1" t="inlineStr">
@@ -11439,15 +10991,13 @@
           <t>1773294093505 - 1773294096904</t>
         </is>
       </c>
-      <c r="D71" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage434.png</t>
-        </is>
-      </c>
-      <c r="E71" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage435.png</t>
-        </is>
+      <c r="D71" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image434.png")</f>
+        <v/>
+      </c>
+      <c r="E71" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image435.png")</f>
+        <v/>
       </c>
       <c r="F71" s="56" t="n"/>
       <c r="G71" s="1" t="inlineStr">
@@ -11481,15 +11031,13 @@
           <t>1773294097904 - 1773294099605</t>
         </is>
       </c>
-      <c r="D73" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage436.png</t>
-        </is>
-      </c>
-      <c r="E73" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage437.png</t>
-        </is>
+      <c r="D73" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image436.png")</f>
+        <v/>
+      </c>
+      <c r="E73" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image437.png")</f>
+        <v/>
       </c>
       <c r="F73" s="56" t="n"/>
       <c r="G73" s="1" t="inlineStr">
@@ -11523,15 +11071,13 @@
           <t>1773294111804 - 1773294112804</t>
         </is>
       </c>
-      <c r="D75" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage438.png</t>
-        </is>
-      </c>
-      <c r="E75" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage439.png</t>
-        </is>
+      <c r="D75" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image438.png")</f>
+        <v/>
+      </c>
+      <c r="E75" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image439.png")</f>
+        <v/>
       </c>
       <c r="F75" s="56" t="n"/>
       <c r="G75" s="1" t="inlineStr">
@@ -11565,15 +11111,13 @@
           <t>1773294115104 -  1773294116004, 1773294118104</t>
         </is>
       </c>
-      <c r="D77" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage440.png</t>
-        </is>
-      </c>
-      <c r="E77" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage441.png</t>
-        </is>
+      <c r="D77" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image440.png")</f>
+        <v/>
+      </c>
+      <c r="E77" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image441.png")</f>
+        <v/>
       </c>
       <c r="F77" s="42" t="n"/>
       <c r="G77" s="7" t="inlineStr">
@@ -11598,15 +11142,13 @@
           <t>1773294118705 - 1773294120605</t>
         </is>
       </c>
-      <c r="D78" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage442.png</t>
-        </is>
-      </c>
-      <c r="E78" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage443.png</t>
-        </is>
+      <c r="D78" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image442.png")</f>
+        <v/>
+      </c>
+      <c r="E78" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image443.png")</f>
+        <v/>
       </c>
       <c r="F78" s="56" t="n"/>
       <c r="G78" s="1" t="inlineStr">
@@ -11640,15 +11182,13 @@
           <t>1773294121704 - 1773294122604</t>
         </is>
       </c>
-      <c r="D80" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage444.png</t>
-        </is>
-      </c>
-      <c r="E80" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage445.png</t>
-        </is>
+      <c r="D80" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image444.png")</f>
+        <v/>
+      </c>
+      <c r="E80" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image445.png")</f>
+        <v/>
       </c>
       <c r="F80" s="42" t="n"/>
       <c r="G80" s="7" t="inlineStr">
@@ -11673,15 +11213,13 @@
           <t>1773294124704 - 1773294125604</t>
         </is>
       </c>
-      <c r="D81" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage446.png</t>
-        </is>
-      </c>
-      <c r="E81" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage447.png</t>
-        </is>
+      <c r="D81" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image446.png")</f>
+        <v/>
+      </c>
+      <c r="E81" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image447.png")</f>
+        <v/>
       </c>
       <c r="F81" s="56" t="n"/>
       <c r="G81" s="1" t="inlineStr">
@@ -11715,15 +11253,13 @@
           <t>1773294125704 - 1773294126605</t>
         </is>
       </c>
-      <c r="D83" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage448.png</t>
-        </is>
-      </c>
-      <c r="E83" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage449.png</t>
-        </is>
+      <c r="D83" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image448.png")</f>
+        <v/>
+      </c>
+      <c r="E83" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image449.png")</f>
+        <v/>
       </c>
       <c r="F83" s="56" t="n"/>
       <c r="G83" s="1" t="inlineStr">
@@ -11757,15 +11293,13 @@
           <t xml:space="preserve">1773294130704 - 1773294132604 </t>
         </is>
       </c>
-      <c r="D85" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage450.png</t>
-        </is>
-      </c>
-      <c r="E85" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage451.png</t>
-        </is>
+      <c r="D85" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image450.png")</f>
+        <v/>
+      </c>
+      <c r="E85" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image451.png")</f>
+        <v/>
       </c>
       <c r="F85" s="42" t="n"/>
       <c r="G85" s="7" t="inlineStr">
@@ -11788,15 +11322,13 @@
       <c r="C86" s="16" t="n">
         <v>1773294135404</v>
       </c>
-      <c r="D86" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage452.png</t>
-        </is>
-      </c>
-      <c r="E86" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage453.png</t>
-        </is>
+      <c r="D86" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image452.png")</f>
+        <v/>
+      </c>
+      <c r="E86" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image453.png")</f>
+        <v/>
       </c>
       <c r="F86" s="42" t="n"/>
       <c r="G86" s="7" t="inlineStr">
@@ -11821,15 +11353,13 @@
           <t>1773294136705 - 1773294138704</t>
         </is>
       </c>
-      <c r="D87" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage454.png</t>
-        </is>
-      </c>
-      <c r="E87" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage455.png</t>
-        </is>
+      <c r="D87" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image454.png")</f>
+        <v/>
+      </c>
+      <c r="E87" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image455.png")</f>
+        <v/>
       </c>
       <c r="F87" s="42" t="n"/>
       <c r="G87" s="7" t="inlineStr">
@@ -11854,15 +11384,13 @@
           <t>1773294143905 - 1773294146805</t>
         </is>
       </c>
-      <c r="D88" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage456.png</t>
-        </is>
-      </c>
-      <c r="E88" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage457.png</t>
-        </is>
+      <c r="D88" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image456.png")</f>
+        <v/>
+      </c>
+      <c r="E88" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image457.png")</f>
+        <v/>
       </c>
       <c r="F88" s="42" t="n"/>
       <c r="G88" s="7" t="inlineStr">
@@ -11887,15 +11415,13 @@
           <t>1773294145905 - 1773294146505</t>
         </is>
       </c>
-      <c r="D89" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage458.png</t>
-        </is>
-      </c>
-      <c r="E89" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage459.png</t>
-        </is>
+      <c r="D89" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image458.png")</f>
+        <v/>
+      </c>
+      <c r="E89" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image459.png")</f>
+        <v/>
       </c>
       <c r="F89" s="42" t="n"/>
       <c r="G89" s="7" t="inlineStr">
@@ -11920,15 +11446,13 @@
           <t>1773294146904 - 1773294149804</t>
         </is>
       </c>
-      <c r="D90" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage460.png</t>
-        </is>
-      </c>
-      <c r="E90" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage461.png</t>
-        </is>
+      <c r="D90" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image460.png")</f>
+        <v/>
+      </c>
+      <c r="E90" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image461.png")</f>
+        <v/>
       </c>
       <c r="F90" s="42" t="n"/>
       <c r="G90" s="7" t="inlineStr">
@@ -11951,15 +11475,13 @@
       <c r="C91" s="16" t="n">
         <v>1773294153805</v>
       </c>
-      <c r="D91" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage462.png</t>
-        </is>
-      </c>
-      <c r="E91" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage463.png</t>
-        </is>
+      <c r="D91" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image462.png")</f>
+        <v/>
+      </c>
+      <c r="E91" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image463.png")</f>
+        <v/>
       </c>
       <c r="F91" s="42" t="n"/>
       <c r="G91" s="7" t="inlineStr">
@@ -11984,15 +11506,13 @@
           <t>1773294160304 - 1773294160704</t>
         </is>
       </c>
-      <c r="D92" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage464.png</t>
-        </is>
-      </c>
-      <c r="E92" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage465.png</t>
-        </is>
+      <c r="D92" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image464.png")</f>
+        <v/>
+      </c>
+      <c r="E92" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image465.png")</f>
+        <v/>
       </c>
       <c r="F92" s="56" t="n"/>
       <c r="G92" s="1" t="inlineStr">
@@ -12024,15 +11544,13 @@
       <c r="C94" s="16" t="n">
         <v>1773294162004</v>
       </c>
-      <c r="D94" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage466.png</t>
-        </is>
-      </c>
-      <c r="E94" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage467.png</t>
-        </is>
+      <c r="D94" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image466.png")</f>
+        <v/>
+      </c>
+      <c r="E94" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image467.png")</f>
+        <v/>
       </c>
       <c r="F94" s="42" t="n"/>
       <c r="G94" s="7" t="inlineStr">
@@ -12057,15 +11575,13 @@
           <t>1773294162805 - 1773294163705</t>
         </is>
       </c>
-      <c r="D95" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage468.png</t>
-        </is>
-      </c>
-      <c r="E95" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage469.png</t>
-        </is>
+      <c r="D95" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image468.png")</f>
+        <v/>
+      </c>
+      <c r="E95" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image469.png")</f>
+        <v/>
       </c>
       <c r="F95" s="42" t="n"/>
       <c r="G95" s="7" t="inlineStr">
@@ -12090,15 +11606,13 @@
           <t>1773294164805 - 1773294165704</t>
         </is>
       </c>
-      <c r="D96" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage470.png</t>
-        </is>
-      </c>
-      <c r="E96" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage471.png</t>
-        </is>
+      <c r="D96" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image470.png")</f>
+        <v/>
+      </c>
+      <c r="E96" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image471.png")</f>
+        <v/>
       </c>
       <c r="F96" s="56" t="n"/>
       <c r="G96" s="1" t="inlineStr">
@@ -12132,15 +11646,13 @@
           <t>1773294165804 - 1773294166405</t>
         </is>
       </c>
-      <c r="D98" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage470.png</t>
-        </is>
-      </c>
-      <c r="E98" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage471.png</t>
-        </is>
+      <c r="D98" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image470.png")</f>
+        <v/>
+      </c>
+      <c r="E98" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image471.png")</f>
+        <v/>
       </c>
       <c r="F98" s="42" t="n"/>
       <c r="G98" s="7" t="inlineStr">
@@ -12165,15 +11677,13 @@
           <t>1773294167704 - 1773294169604</t>
         </is>
       </c>
-      <c r="D99" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage472.png</t>
-        </is>
-      </c>
-      <c r="E99" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage473.png</t>
-        </is>
+      <c r="D99" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image472.png")</f>
+        <v/>
+      </c>
+      <c r="E99" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image473.png")</f>
+        <v/>
       </c>
       <c r="F99" s="42" t="n"/>
       <c r="G99" s="7" t="inlineStr">
@@ -12198,15 +11708,13 @@
           <t>1773294170004 - 1773294170204</t>
         </is>
       </c>
-      <c r="D100" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage474.png</t>
-        </is>
-      </c>
-      <c r="E100" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage475.png</t>
-        </is>
+      <c r="D100" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image474.png")</f>
+        <v/>
+      </c>
+      <c r="E100" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image475.png")</f>
+        <v/>
       </c>
       <c r="F100" s="42" t="n"/>
       <c r="G100" s="7" t="inlineStr">
@@ -12231,15 +11739,13 @@
           <t>1773294170704 - 1773294171605</t>
         </is>
       </c>
-      <c r="D101" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage476.png</t>
-        </is>
-      </c>
-      <c r="E101" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage477.png</t>
-        </is>
+      <c r="D101" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image476.png")</f>
+        <v/>
+      </c>
+      <c r="E101" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image477.png")</f>
+        <v/>
       </c>
       <c r="F101" s="42" t="n"/>
       <c r="G101" s="7" t="inlineStr">
@@ -12264,15 +11770,13 @@
           <t>1773294171705 - 1773294172605</t>
         </is>
       </c>
-      <c r="D102" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage478.png</t>
-        </is>
-      </c>
-      <c r="E102" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage479.png</t>
-        </is>
+      <c r="D102" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image478.png")</f>
+        <v/>
+      </c>
+      <c r="E102" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image479.png")</f>
+        <v/>
       </c>
       <c r="F102" s="42" t="n"/>
       <c r="G102" s="7" t="inlineStr">
@@ -12297,15 +11801,13 @@
           <t>1773294173705 - 1773294174704</t>
         </is>
       </c>
-      <c r="D103" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage480.png</t>
-        </is>
-      </c>
-      <c r="E103" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage481.png</t>
-        </is>
+      <c r="D103" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image480.png")</f>
+        <v/>
+      </c>
+      <c r="E103" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image481.png")</f>
+        <v/>
       </c>
       <c r="F103" s="42" t="n"/>
       <c r="G103" s="7" t="inlineStr">
@@ -12330,15 +11832,13 @@
           <t>1773294174804 - 1773294175704</t>
         </is>
       </c>
-      <c r="D104" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage482.png</t>
-        </is>
-      </c>
-      <c r="E104" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage483.png</t>
-        </is>
+      <c r="D104" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image482.png")</f>
+        <v/>
+      </c>
+      <c r="E104" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image483.png")</f>
+        <v/>
       </c>
       <c r="F104" s="42" t="n"/>
       <c r="G104" s="7" t="inlineStr">
@@ -12363,15 +11863,13 @@
           <t xml:space="preserve">1773294175804 - 1773294176704 </t>
         </is>
       </c>
-      <c r="D105" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage484.png</t>
-        </is>
-      </c>
-      <c r="E105" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage481.png</t>
-        </is>
+      <c r="D105" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image484.png")</f>
+        <v/>
+      </c>
+      <c r="E105" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image481.png")</f>
+        <v/>
       </c>
       <c r="F105" s="42" t="n"/>
       <c r="G105" s="7" t="inlineStr">
@@ -12396,15 +11894,13 @@
           <t>1773294176804 - 1773294177704</t>
         </is>
       </c>
-      <c r="D106" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage485.png</t>
-        </is>
-      </c>
-      <c r="E106" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage486.png</t>
-        </is>
+      <c r="D106" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image485.png")</f>
+        <v/>
+      </c>
+      <c r="E106" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image486.png")</f>
+        <v/>
       </c>
       <c r="F106" s="56" t="n"/>
       <c r="G106" s="1" t="inlineStr">
@@ -12438,15 +11934,13 @@
           <t>1773294177804 - 1773294179705</t>
         </is>
       </c>
-      <c r="D108" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage487.png</t>
-        </is>
-      </c>
-      <c r="E108" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage488.png</t>
-        </is>
+      <c r="D108" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image487.png")</f>
+        <v/>
+      </c>
+      <c r="E108" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image488.png")</f>
+        <v/>
       </c>
       <c r="F108" s="56" t="n"/>
       <c r="G108" s="1" t="inlineStr">
@@ -12480,15 +11974,13 @@
           <t>1773294180905 - 1773294181805</t>
         </is>
       </c>
-      <c r="D110" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage489.png</t>
-        </is>
-      </c>
-      <c r="E110" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage490.png</t>
-        </is>
+      <c r="D110" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image489.png")</f>
+        <v/>
+      </c>
+      <c r="E110" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image490.png")</f>
+        <v/>
       </c>
       <c r="F110" s="42" t="n"/>
       <c r="G110" s="7" t="inlineStr">
@@ -12513,15 +12005,13 @@
           <t>1773294182904 - 1773294183804</t>
         </is>
       </c>
-      <c r="D111" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage491.png</t>
-        </is>
-      </c>
-      <c r="E111" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage492.png</t>
-        </is>
+      <c r="D111" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image491.png")</f>
+        <v/>
+      </c>
+      <c r="E111" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image492.png")</f>
+        <v/>
       </c>
       <c r="F111" s="56" t="n"/>
       <c r="G111" s="1" t="inlineStr">
@@ -12555,15 +12045,13 @@
           <t>1773294183904 - 1773294184804</t>
         </is>
       </c>
-      <c r="D113" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage493.png</t>
-        </is>
-      </c>
-      <c r="E113" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage494.png</t>
-        </is>
+      <c r="D113" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image493.png")</f>
+        <v/>
+      </c>
+      <c r="E113" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image494.png")</f>
+        <v/>
       </c>
       <c r="F113" s="56" t="n"/>
       <c r="G113" s="1" t="inlineStr">
@@ -12597,15 +12085,13 @@
           <t>1773294186905 - 1773294187805</t>
         </is>
       </c>
-      <c r="D115" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage495.png</t>
-        </is>
-      </c>
-      <c r="E115" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage496.png</t>
-        </is>
+      <c r="D115" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image495.png")</f>
+        <v/>
+      </c>
+      <c r="E115" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image496.png")</f>
+        <v/>
       </c>
       <c r="F115" s="42" t="n"/>
       <c r="G115" s="7" t="inlineStr">
@@ -12630,15 +12116,13 @@
           <t>1773294187905 - 1773294188805, 1773294189904 - 1773294193204</t>
         </is>
       </c>
-      <c r="D116" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage497.png</t>
-        </is>
-      </c>
-      <c r="E116" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage498.png</t>
-        </is>
+      <c r="D116" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image497.png")</f>
+        <v/>
+      </c>
+      <c r="E116" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image498.png")</f>
+        <v/>
       </c>
       <c r="F116" s="56" t="n"/>
       <c r="G116" s="1" t="inlineStr">
@@ -12672,15 +12156,13 @@
           <t>1773294193304 - 1773294194404</t>
         </is>
       </c>
-      <c r="D118" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage499.png</t>
-        </is>
-      </c>
-      <c r="E118" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage500.png</t>
-        </is>
+      <c r="D118" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image499.png")</f>
+        <v/>
+      </c>
+      <c r="E118" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image500.png")</f>
+        <v/>
       </c>
       <c r="F118" s="42" t="n"/>
       <c r="G118" s="7" t="inlineStr">
@@ -12705,15 +12187,13 @@
           <t>1773294194605 - 1773294195805</t>
         </is>
       </c>
-      <c r="D119" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage501.png</t>
-        </is>
-      </c>
-      <c r="E119" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage502.png</t>
-        </is>
+      <c r="D119" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image501.png")</f>
+        <v/>
+      </c>
+      <c r="E119" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image502.png")</f>
+        <v/>
       </c>
       <c r="F119" s="42" t="n"/>
       <c r="G119" s="7" t="inlineStr">
@@ -12738,15 +12218,13 @@
           <t>1773294196805, 1773294197305, 1773294197704, 1773294197904, 1773294198305</t>
         </is>
       </c>
-      <c r="D120" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage503.png</t>
-        </is>
-      </c>
-      <c r="E120" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage504.png</t>
-        </is>
+      <c r="D120" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image503.png")</f>
+        <v/>
+      </c>
+      <c r="E120" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image504.png")</f>
+        <v/>
       </c>
       <c r="F120" s="42" t="n"/>
       <c r="G120" s="7" t="inlineStr">
@@ -12771,15 +12249,13 @@
           <t>1773294257800 - 1773294263500</t>
         </is>
       </c>
-      <c r="D121" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage505.png</t>
-        </is>
-      </c>
-      <c r="E121" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage506.png</t>
-        </is>
+      <c r="D121" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image505.png")</f>
+        <v/>
+      </c>
+      <c r="E121" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image506.png")</f>
+        <v/>
       </c>
       <c r="F121" s="42" t="n"/>
       <c r="G121" s="7" t="inlineStr">
@@ -12804,15 +12280,13 @@
           <t>1773294291805, 1773294292104 - 1773294293505</t>
         </is>
       </c>
-      <c r="D122" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage507.png</t>
-        </is>
-      </c>
-      <c r="E122" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage508.png</t>
-        </is>
+      <c r="D122" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image507.png")</f>
+        <v/>
+      </c>
+      <c r="E122" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image508.png")</f>
+        <v/>
       </c>
       <c r="F122" s="42" t="n"/>
       <c r="G122" s="7" t="inlineStr">
@@ -12837,15 +12311,13 @@
           <t>1773294301505 - 1773294302305</t>
         </is>
       </c>
-      <c r="D123" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage509.png</t>
-        </is>
-      </c>
-      <c r="E123" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage510.png</t>
-        </is>
+      <c r="D123" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image509.png")</f>
+        <v/>
+      </c>
+      <c r="E123" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image510.png")</f>
+        <v/>
       </c>
       <c r="F123" s="56" t="n"/>
       <c r="G123" s="1" t="inlineStr">
@@ -12879,15 +12351,13 @@
           <t>1773294302405 - 1773294303504</t>
         </is>
       </c>
-      <c r="D125" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage511.png</t>
-        </is>
-      </c>
-      <c r="E125" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage512.png</t>
-        </is>
+      <c r="D125" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image511.png")</f>
+        <v/>
+      </c>
+      <c r="E125" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image512.png")</f>
+        <v/>
       </c>
       <c r="F125" s="42" t="n"/>
       <c r="G125" s="7" t="inlineStr">
@@ -12912,20 +12382,17 @@
           <t>1773294304804 - 1773294307304</t>
         </is>
       </c>
-      <c r="D126" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage513.png</t>
-        </is>
-      </c>
-      <c r="E126" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage514.png</t>
-        </is>
-      </c>
-      <c r="F126" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage515.png</t>
-        </is>
+      <c r="D126" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image513.png")</f>
+        <v/>
+      </c>
+      <c r="E126" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image514.png")</f>
+        <v/>
+      </c>
+      <c r="F126" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image515.png")</f>
+        <v/>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
@@ -12949,15 +12416,13 @@
           <t>1773294308605 - 1773294309704</t>
         </is>
       </c>
-      <c r="D127" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage516.png</t>
-        </is>
-      </c>
-      <c r="E127" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage517.png</t>
-        </is>
+      <c r="D127" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image516.png")</f>
+        <v/>
+      </c>
+      <c r="E127" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image517.png")</f>
+        <v/>
       </c>
       <c r="F127" s="42" t="n"/>
       <c r="G127" s="7" t="inlineStr">
@@ -12982,15 +12447,13 @@
           <t>1773294310904 - 1773294313704</t>
         </is>
       </c>
-      <c r="D128" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage518.png</t>
-        </is>
-      </c>
-      <c r="E128" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage519.png</t>
-        </is>
+      <c r="D128" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image518.png")</f>
+        <v/>
+      </c>
+      <c r="E128" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image519.png")</f>
+        <v/>
       </c>
       <c r="F128" s="56" t="n"/>
       <c r="G128" s="1" t="inlineStr">
@@ -13024,15 +12487,13 @@
           <t>1773294320905 - 1773294324604</t>
         </is>
       </c>
-      <c r="D130" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage520.png</t>
-        </is>
-      </c>
-      <c r="E130" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage521.png</t>
-        </is>
+      <c r="D130" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image520.png")</f>
+        <v/>
+      </c>
+      <c r="E130" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image521.png")</f>
+        <v/>
       </c>
       <c r="F130" s="42" t="n"/>
       <c r="G130" s="7" t="inlineStr">
@@ -13057,15 +12518,13 @@
           <t>1773294331305, 1773294331405, 1773294331505, 1773294331705, 1773294331904, 1773294332005, 1773294332105</t>
         </is>
       </c>
-      <c r="D131" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage522.png</t>
-        </is>
-      </c>
-      <c r="E131" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage523.png</t>
-        </is>
+      <c r="D131" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image522.png")</f>
+        <v/>
+      </c>
+      <c r="E131" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image523.png")</f>
+        <v/>
       </c>
       <c r="F131" s="42" t="n"/>
       <c r="G131" s="7" t="inlineStr">
@@ -13090,15 +12549,13 @@
           <t>1773294334604 - 1773294335804</t>
         </is>
       </c>
-      <c r="D132" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage524.png</t>
-        </is>
-      </c>
-      <c r="E132" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage525.png</t>
-        </is>
+      <c r="D132" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image524.png")</f>
+        <v/>
+      </c>
+      <c r="E132" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image525.png")</f>
+        <v/>
       </c>
       <c r="F132" s="42" t="n"/>
       <c r="G132" s="7" t="inlineStr">
@@ -13123,15 +12580,13 @@
           <t>1773294336604 - 1773294339005</t>
         </is>
       </c>
-      <c r="D133" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage526.png</t>
-        </is>
-      </c>
-      <c r="E133" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage527.png</t>
-        </is>
+      <c r="D133" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image526.png")</f>
+        <v/>
+      </c>
+      <c r="E133" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image527.png")</f>
+        <v/>
       </c>
       <c r="F133" s="42" t="n"/>
       <c r="G133" s="7" t="inlineStr">
@@ -13156,15 +12611,13 @@
           <t>1773294341404, 1773294341804 - 1773294342404</t>
         </is>
       </c>
-      <c r="D134" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage528.png</t>
-        </is>
-      </c>
-      <c r="E134" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage529.png</t>
-        </is>
+      <c r="D134" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image528.png")</f>
+        <v/>
+      </c>
+      <c r="E134" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image529.png")</f>
+        <v/>
       </c>
       <c r="F134" s="42" t="n"/>
       <c r="G134" s="7" t="inlineStr">
@@ -13189,15 +12642,13 @@
           <t>1773294343404 - 1773294344104</t>
         </is>
       </c>
-      <c r="D135" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage530.png</t>
-        </is>
-      </c>
-      <c r="E135" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage531.png</t>
-        </is>
+      <c r="D135" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image530.png")</f>
+        <v/>
+      </c>
+      <c r="E135" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image531.png")</f>
+        <v/>
       </c>
       <c r="F135" s="42" t="n"/>
       <c r="G135" s="7" t="inlineStr">
@@ -13222,15 +12673,13 @@
           <t>1773294349004 - 1773294350004</t>
         </is>
       </c>
-      <c r="D136" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage532.png</t>
-        </is>
-      </c>
-      <c r="E136" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage533.png</t>
-        </is>
+      <c r="D136" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image532.png")</f>
+        <v/>
+      </c>
+      <c r="E136" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image533.png")</f>
+        <v/>
       </c>
       <c r="F136" s="42" t="n"/>
       <c r="G136" s="7" t="inlineStr">
@@ -13255,15 +12704,13 @@
           <t>1773294353205 - 1773294355305</t>
         </is>
       </c>
-      <c r="D137" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage534.png</t>
-        </is>
-      </c>
-      <c r="E137" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage535.png</t>
-        </is>
+      <c r="D137" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image534.png")</f>
+        <v/>
+      </c>
+      <c r="E137" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image535.png")</f>
+        <v/>
       </c>
       <c r="F137" s="56" t="n"/>
       <c r="G137" s="1" t="inlineStr">
@@ -13297,15 +12744,13 @@
           <t>1773294355404 - 1773294356504</t>
         </is>
       </c>
-      <c r="D139" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage536.png</t>
-        </is>
-      </c>
-      <c r="E139" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage537.png</t>
-        </is>
+      <c r="D139" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image536.png")</f>
+        <v/>
+      </c>
+      <c r="E139" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image537.png")</f>
+        <v/>
       </c>
       <c r="F139" s="56" t="n"/>
       <c r="G139" s="1" t="inlineStr">
@@ -13339,15 +12784,13 @@
           <t>1773294359505 - 1773294360305</t>
         </is>
       </c>
-      <c r="D141" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage538.png</t>
-        </is>
-      </c>
-      <c r="E141" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage539.png</t>
-        </is>
+      <c r="D141" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image538.png")</f>
+        <v/>
+      </c>
+      <c r="E141" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image539.png")</f>
+        <v/>
       </c>
       <c r="F141" s="42" t="n"/>
       <c r="G141" s="7" t="inlineStr">
@@ -13372,10 +12815,9 @@
           <t>1773294363003, 1773294372203</t>
         </is>
       </c>
-      <c r="D142" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage540.png</t>
-        </is>
+      <c r="D142" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image540.png")</f>
+        <v/>
       </c>
       <c r="E142" s="42" t="n"/>
       <c r="F142" s="42" t="n"/>
@@ -13401,15 +12843,13 @@
           <t>1773294373004, 1773294373905</t>
         </is>
       </c>
-      <c r="D143" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage541.png</t>
-        </is>
-      </c>
-      <c r="E143" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage542.png</t>
-        </is>
+      <c r="D143" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image541.png")</f>
+        <v/>
+      </c>
+      <c r="E143" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image542.png")</f>
+        <v/>
       </c>
       <c r="F143" s="42" t="n"/>
       <c r="G143" s="7" t="inlineStr">
@@ -13434,15 +12874,13 @@
           <t>1773294374605 - 1773294374905</t>
         </is>
       </c>
-      <c r="D144" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage543.png</t>
-        </is>
-      </c>
-      <c r="E144" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage544.png</t>
-        </is>
+      <c r="D144" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image543.png")</f>
+        <v/>
+      </c>
+      <c r="E144" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image544.png")</f>
+        <v/>
       </c>
       <c r="F144" s="42" t="n"/>
       <c r="G144" s="7" t="inlineStr">
@@ -13465,10 +12903,9 @@
       <c r="C145" s="16" t="n">
         <v>1773294375004</v>
       </c>
-      <c r="D145" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage545.png</t>
-        </is>
+      <c r="D145" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image545.png")</f>
+        <v/>
       </c>
       <c r="E145" s="42" t="n"/>
       <c r="F145" s="42" t="n"/>
@@ -13494,15 +12931,13 @@
           <t>1773294375104, 1773294375205, 1773294375305</t>
         </is>
       </c>
-      <c r="D146" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage546.png</t>
-        </is>
-      </c>
-      <c r="E146" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage547.png</t>
-        </is>
+      <c r="D146" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image546.png")</f>
+        <v/>
+      </c>
+      <c r="E146" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image547.png")</f>
+        <v/>
       </c>
       <c r="F146" s="56" t="n"/>
       <c r="G146" s="1" t="inlineStr">
@@ -13536,15 +12971,13 @@
           <t>1773294376205 - 1773294377005</t>
         </is>
       </c>
-      <c r="D148" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage548.png</t>
-        </is>
-      </c>
-      <c r="E148" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage549.png</t>
-        </is>
+      <c r="D148" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image548.png")</f>
+        <v/>
+      </c>
+      <c r="E148" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image549.png")</f>
+        <v/>
       </c>
       <c r="F148" s="42" t="n"/>
       <c r="G148" s="7" t="inlineStr">
@@ -13569,15 +13002,13 @@
           <t>1773294379504, 1773294380604</t>
         </is>
       </c>
-      <c r="D149" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage550.png</t>
-        </is>
-      </c>
-      <c r="E149" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage551.png</t>
-        </is>
+      <c r="D149" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image550.png")</f>
+        <v/>
+      </c>
+      <c r="E149" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image551.png")</f>
+        <v/>
       </c>
       <c r="F149" s="42" t="n"/>
       <c r="G149" s="7" t="inlineStr">
@@ -13602,15 +13033,13 @@
           <t>1773294390904 - 1773294391704</t>
         </is>
       </c>
-      <c r="D150" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage552.png</t>
-        </is>
-      </c>
-      <c r="E150" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage553.png</t>
-        </is>
+      <c r="D150" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image552.png")</f>
+        <v/>
+      </c>
+      <c r="E150" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image553.png")</f>
+        <v/>
       </c>
       <c r="F150" s="42" t="n"/>
       <c r="G150" s="7" t="inlineStr">
@@ -13633,10 +13062,9 @@
       <c r="C151" s="16" t="n">
         <v>1773294394003</v>
       </c>
-      <c r="D151" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage554.png</t>
-        </is>
+      <c r="D151" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image554.png")</f>
+        <v/>
       </c>
       <c r="E151" s="42" t="n"/>
       <c r="F151" s="42" t="n"/>
@@ -13660,10 +13088,9 @@
       <c r="C152" s="16" t="n">
         <v>1773294394503</v>
       </c>
-      <c r="D152" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage555.png</t>
-        </is>
+      <c r="D152" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image555.png")</f>
+        <v/>
       </c>
       <c r="E152" s="42" t="n"/>
       <c r="F152" s="42" t="n"/>
@@ -13689,15 +13116,13 @@
           <t>1773294394704 - 1773294395404, 1773294398305 - 1773294399105</t>
         </is>
       </c>
-      <c r="D153" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage556.png</t>
-        </is>
-      </c>
-      <c r="E153" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage557.png</t>
-        </is>
+      <c r="D153" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image556.png")</f>
+        <v/>
+      </c>
+      <c r="E153" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image557.png")</f>
+        <v/>
       </c>
       <c r="F153" s="42" t="n"/>
       <c r="G153" s="7" t="inlineStr">
@@ -13722,15 +13147,13 @@
           <t>1773294399205 - 1773294399904</t>
         </is>
       </c>
-      <c r="D154" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage558.png</t>
-        </is>
-      </c>
-      <c r="E154" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage559.png</t>
-        </is>
+      <c r="D154" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image558.png")</f>
+        <v/>
+      </c>
+      <c r="E154" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image559.png")</f>
+        <v/>
       </c>
       <c r="F154" s="42" t="n"/>
       <c r="G154" s="7" t="inlineStr">
@@ -13755,15 +13178,13 @@
           <t>1773294401905 - 1773294402705, 1773294405604 - 1773294406304</t>
         </is>
       </c>
-      <c r="D155" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage560.png</t>
-        </is>
-      </c>
-      <c r="E155" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage561.png</t>
-        </is>
+      <c r="D155" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image560.png")</f>
+        <v/>
+      </c>
+      <c r="E155" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image561.png")</f>
+        <v/>
       </c>
       <c r="F155" s="56" t="n"/>
       <c r="G155" s="1" t="inlineStr">
@@ -13797,15 +13218,13 @@
           <t>1773294408204 - 1773294409204</t>
         </is>
       </c>
-      <c r="D157" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage562.png</t>
-        </is>
-      </c>
-      <c r="E157" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage563.png</t>
-        </is>
+      <c r="D157" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image562.png")</f>
+        <v/>
+      </c>
+      <c r="E157" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image563.png")</f>
+        <v/>
       </c>
       <c r="F157" s="56" t="n"/>
       <c r="G157" s="1" t="inlineStr">
@@ -13839,15 +13258,13 @@
           <t>1773294410205 - 1773294412005</t>
         </is>
       </c>
-      <c r="D159" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage564.png</t>
-        </is>
-      </c>
-      <c r="E159" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage565.png</t>
-        </is>
+      <c r="D159" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image564.png")</f>
+        <v/>
+      </c>
+      <c r="E159" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image565.png")</f>
+        <v/>
       </c>
       <c r="F159" s="42" t="n"/>
       <c r="G159" s="7" t="inlineStr">
@@ -13872,10 +13289,9 @@
           <t>1773294413703, 1773294414203</t>
         </is>
       </c>
-      <c r="D160" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage566.png</t>
-        </is>
+      <c r="D160" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image566.png")</f>
+        <v/>
       </c>
       <c r="E160" s="42" t="n"/>
       <c r="F160" s="42" t="n"/>
@@ -13899,15 +13315,13 @@
       <c r="C161" s="16" t="n">
         <v>1773294417405</v>
       </c>
-      <c r="D161" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage567.png</t>
-        </is>
-      </c>
-      <c r="E161" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage568.png</t>
-        </is>
+      <c r="D161" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image567.png")</f>
+        <v/>
+      </c>
+      <c r="E161" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image568.png")</f>
+        <v/>
       </c>
       <c r="F161" s="42" t="n"/>
       <c r="G161" s="7" t="inlineStr">
@@ -13932,15 +13346,13 @@
           <t>1773294422104 - 1773294423505</t>
         </is>
       </c>
-      <c r="D162" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage569.png</t>
-        </is>
-      </c>
-      <c r="E162" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage570.png</t>
-        </is>
+      <c r="D162" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image569.png")</f>
+        <v/>
+      </c>
+      <c r="E162" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image570.png")</f>
+        <v/>
       </c>
       <c r="F162" s="56" t="n"/>
       <c r="G162" s="1" t="inlineStr">
@@ -13974,15 +13386,13 @@
           <t>1773294427404 - 1773294431005</t>
         </is>
       </c>
-      <c r="D164" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage571.png</t>
-        </is>
-      </c>
-      <c r="E164" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage572.png</t>
-        </is>
+      <c r="D164" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image571.png")</f>
+        <v/>
+      </c>
+      <c r="E164" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image572.png")</f>
+        <v/>
       </c>
       <c r="F164" s="42" t="n"/>
       <c r="G164" s="7" t="inlineStr">
@@ -14007,15 +13417,13 @@
           <t>1773294431204 - 1773294432604</t>
         </is>
       </c>
-      <c r="D165" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage573.png</t>
-        </is>
-      </c>
-      <c r="E165" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage574.png</t>
-        </is>
+      <c r="D165" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image573.png")</f>
+        <v/>
+      </c>
+      <c r="E165" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image574.png")</f>
+        <v/>
       </c>
       <c r="F165" s="42" t="n"/>
       <c r="G165" s="7" t="inlineStr">
@@ -14040,15 +13448,13 @@
           <t>1773294432804 - 1773294434605</t>
         </is>
       </c>
-      <c r="D166" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage575.png</t>
-        </is>
-      </c>
-      <c r="E166" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage576.png</t>
-        </is>
+      <c r="D166" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image575.png")</f>
+        <v/>
+      </c>
+      <c r="E166" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image576.png")</f>
+        <v/>
       </c>
       <c r="F166" s="42" t="n"/>
       <c r="G166" s="7" t="inlineStr">
@@ -14073,15 +13479,13 @@
           <t>1773294434805 - 1773294435904</t>
         </is>
       </c>
-      <c r="D167" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage577.png</t>
-        </is>
-      </c>
-      <c r="E167" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage578.png</t>
-        </is>
+      <c r="D167" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image577.png")</f>
+        <v/>
+      </c>
+      <c r="E167" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image578.png")</f>
+        <v/>
       </c>
       <c r="F167" s="42" t="n"/>
       <c r="G167" s="7" t="inlineStr">
@@ -14106,15 +13510,13 @@
           <t>1773294438904 - 1773294440204</t>
         </is>
       </c>
-      <c r="D168" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage579.png</t>
-        </is>
-      </c>
-      <c r="E168" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage580.png</t>
-        </is>
+      <c r="D168" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image579.png")</f>
+        <v/>
+      </c>
+      <c r="E168" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image580.png")</f>
+        <v/>
       </c>
       <c r="F168" s="42" t="n"/>
       <c r="G168" s="7" t="inlineStr">
@@ -14139,15 +13541,13 @@
           <t>1773294443105 - 1773294444204</t>
         </is>
       </c>
-      <c r="D169" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage581.png</t>
-        </is>
-      </c>
-      <c r="E169" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage582.png</t>
-        </is>
+      <c r="D169" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image581.png")</f>
+        <v/>
+      </c>
+      <c r="E169" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image582.png")</f>
+        <v/>
       </c>
       <c r="F169" s="42" t="n"/>
       <c r="G169" s="7" t="inlineStr">
@@ -14172,15 +13572,13 @@
           <t>1773294448105 - 1773294449405, 1773294450504 - 1773294451504</t>
         </is>
       </c>
-      <c r="D170" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage583.png</t>
-        </is>
-      </c>
-      <c r="E170" s="56" t="inlineStr">
-        <is>
-          <t>replaced with urlimage584.png</t>
-        </is>
+      <c r="D170" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image583.png")</f>
+        <v/>
+      </c>
+      <c r="E170" s="56">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image584.png")</f>
+        <v/>
       </c>
       <c r="F170" s="56" t="n"/>
       <c r="G170" s="1" t="inlineStr">
@@ -14214,15 +13612,13 @@
           <t>1773294451604 - 1773294452704</t>
         </is>
       </c>
-      <c r="D172" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage585.png</t>
-        </is>
-      </c>
-      <c r="E172" s="42" t="inlineStr">
-        <is>
-          <t>replaced with urlimage586.png</t>
-        </is>
+      <c r="D172" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image585.png")</f>
+        <v/>
+      </c>
+      <c r="E172" s="42">
+        <f>IMAGE("https://liskibruh.github.io/l4_data_sheets_table_images_mapper/l4_problematic_frames/media/image586.png")</f>
+        <v/>
       </c>
       <c r="F172" s="42" t="n"/>
       <c r="G172" s="7" t="inlineStr">
